--- a/STELLA-1.2/lab_spec_documents/Lab Spec Build Instructions.xlsx
+++ b/STELLA-1.2/lab_spec_documents/Lab Spec Build Instructions.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="267">
   <si>
     <t>STELLA Lab Spec parts</t>
   </si>
@@ -76,7 +76,7 @@
     <t>$ line</t>
   </si>
   <si>
-    <t>.STL</t>
+    <t>.STL details, or link to part</t>
   </si>
   <si>
     <t>C2</t>
@@ -166,9 +166,26 @@
     <t>Proto-Advantage LED2 - DIP adapter</t>
   </si>
   <si>
+    <t>Proto-Advantage</t>
+  </si>
+  <si>
     <t>Proto-Advantage small proto board</t>
   </si>
   <si>
+    <t>SBB1002-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>https://www.proto-advantage.com/store/product_info.php?products_id=200009</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Socket header 3x1 pos </t>
   </si>
   <si>
@@ -184,10 +201,16 @@
     <t>Sparkfun mini proto board</t>
   </si>
   <si>
-    <t>Stacking header 6 pos</t>
-  </si>
-  <si>
-    <t>Stacking headers, 6 pos</t>
+    <t>Socket header 6 pos</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>need to find socket headers of correct height</t>
+  </si>
+  <si>
+    <t>Socket headers, 6 pos</t>
   </si>
   <si>
     <t>White LED panel</t>
@@ -298,9 +321,6 @@
     <t>LS-C2 Cuvette optics</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>LS-C2 Assembly drawing</t>
   </si>
   <si>
@@ -340,6 +360,9 @@
     <t xml:space="preserve">What color? </t>
   </si>
   <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>Get board</t>
   </si>
   <si>
@@ -367,12 +390,15 @@
     <t>Install transistors</t>
   </si>
   <si>
-    <t>2N2222 or PN2222</t>
+    <t>2N2222 or PN2222ABU</t>
   </si>
   <si>
     <t>All flats towards J: B12-13-14; B16-17-18; G12-13-14; G16-17-18</t>
   </si>
   <si>
+    <t>Solder the center pin first, then straighten the body before soldering the other two pins</t>
+  </si>
+  <si>
     <t>Install shunt resistors</t>
   </si>
   <si>
@@ -400,7 +426,10 @@
     <t>C11-E13, C15-E17; H11-J13; H15-J17</t>
   </si>
   <si>
-    <t>Install stacking headers for devices</t>
+    <t xml:space="preserve">49.9Ω in photos. Either value is OK. </t>
+  </si>
+  <si>
+    <t>Install socket headers for devices</t>
   </si>
   <si>
     <t>6 pos, 4 places</t>
@@ -415,13 +444,13 @@
     <t>3x3, 2 places</t>
   </si>
   <si>
-    <t>ON BACK: A, B, C x 1, 2, 3; H, i, J x 1, 2, 3</t>
+    <t>ON BACK: A,B,C x 1,2,3; H,i,J x 1,2,3</t>
   </si>
   <si>
     <t>3 pos, 3 places</t>
   </si>
   <si>
-    <t>ON BACK: SCL 1, 2, 3; GND 1, 2, 3; 3V 1, 2, 3</t>
+    <t>ON BACK: SDA 1,2,3; GND 1,2,3; 3V 1,2,3</t>
   </si>
   <si>
     <t>Install ground wires</t>
@@ -830,7 +859,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -843,6 +872,12 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
@@ -1174,6 +1209,21 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="17"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
         <color indexed="17"/>
       </right>
       <top style="medium">
@@ -1289,28 +1339,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="17"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1395,12 +1430,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1410,6 +1448,9 @@
     <xf numFmtId="0" fontId="0" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1422,25 +1463,37 @@
     <xf numFmtId="0" fontId="0" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="11" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1458,16 +1511,16 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -1482,7 +1535,7 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -3443,7 +3496,9 @@
       <c r="F32" t="s" s="11">
         <v>22</v>
       </c>
-      <c r="G32" s="13"/>
+      <c r="G32" t="s" s="11">
+        <v>41</v>
+      </c>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
       <c r="J32" s="12" cm="1">
@@ -3471,7 +3526,9 @@
       <c r="F33" t="s" s="11">
         <v>22</v>
       </c>
-      <c r="G33" s="13"/>
+      <c r="G33" t="s" s="11">
+        <v>41</v>
+      </c>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
       <c r="J33" s="12" cm="1">
@@ -3488,7 +3545,7 @@
         <v>12</v>
       </c>
       <c r="C34" t="s" s="11">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D34" s="12">
         <v>1</v>
@@ -3499,14 +3556,22 @@
       <c r="F34" t="s" s="11">
         <v>22</v>
       </c>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
+      <c r="G34" t="s" s="11">
+        <v>41</v>
+      </c>
+      <c r="H34" t="s" s="11">
+        <v>43</v>
+      </c>
+      <c r="I34" s="12">
+        <v>1</v>
+      </c>
       <c r="J34" s="12" cm="1">
         <f t="array" ref="J34">I34*D34</f>
-        <v>0</v>
-      </c>
-      <c r="K34" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="K34" t="s" s="11">
+        <v>44</v>
+      </c>
     </row>
     <row r="35" ht="20.05" customHeight="1">
       <c r="A35" s="9">
@@ -3516,7 +3581,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="s" s="11">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D35" s="12">
         <v>1</v>
@@ -3527,14 +3592,22 @@
       <c r="F35" t="s" s="11">
         <v>22</v>
       </c>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
+      <c r="G35" t="s" s="11">
+        <v>41</v>
+      </c>
+      <c r="H35" t="s" s="11">
+        <v>43</v>
+      </c>
+      <c r="I35" s="12">
+        <v>1</v>
+      </c>
       <c r="J35" s="12" cm="1">
         <f t="array" ref="J35">I35*D35</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="K35" t="s" s="11">
+        <v>44</v>
+      </c>
     </row>
     <row r="36" ht="20.05" customHeight="1">
       <c r="A36" s="9">
@@ -3544,7 +3617,7 @@
         <v>19</v>
       </c>
       <c r="C36" t="s" s="11">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D36" s="12">
         <v>1</v>
@@ -3572,7 +3645,7 @@
         <v>19</v>
       </c>
       <c r="C37" t="s" s="11">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D37" s="12">
         <v>1</v>
@@ -3600,7 +3673,7 @@
         <v>19</v>
       </c>
       <c r="C38" t="s" s="11">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D38" s="12">
         <v>2</v>
@@ -3628,7 +3701,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="s" s="11">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D39" s="12">
         <v>1</v>
@@ -3656,7 +3729,7 @@
         <v>12</v>
       </c>
       <c r="C40" t="s" s="11">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D40" s="12">
         <v>2</v>
@@ -3684,7 +3757,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="s" s="11">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D41" s="12">
         <v>1</v>
@@ -3712,7 +3785,7 @@
         <v>12</v>
       </c>
       <c r="C42" t="s" s="11">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D42" s="12">
         <v>1</v>
@@ -3724,13 +3797,17 @@
         <v>22</v>
       </c>
       <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
+      <c r="H42" t="s" s="11">
+        <v>51</v>
+      </c>
       <c r="I42" s="13"/>
       <c r="J42" s="12" cm="1">
         <f t="array" ref="J42">I42*D42</f>
         <v>0</v>
       </c>
-      <c r="K42" s="13"/>
+      <c r="K42" t="s" s="11">
+        <v>52</v>
+      </c>
     </row>
     <row r="43" ht="20.05" customHeight="1">
       <c r="A43" s="9">
@@ -3740,7 +3817,7 @@
         <v>19</v>
       </c>
       <c r="C43" t="s" s="11">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D43" s="12">
         <v>4</v>
@@ -3752,13 +3829,17 @@
         <v>22</v>
       </c>
       <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
+      <c r="H43" t="s" s="11">
+        <v>51</v>
+      </c>
       <c r="I43" s="13"/>
       <c r="J43" s="12" cm="1">
         <f t="array" ref="J43">I43*D43</f>
         <v>0</v>
       </c>
-      <c r="K43" s="13"/>
+      <c r="K43" t="s" s="11">
+        <v>52</v>
+      </c>
     </row>
     <row r="44" ht="20.05" customHeight="1">
       <c r="A44" s="9">
@@ -3768,7 +3849,7 @@
         <v>12</v>
       </c>
       <c r="C44" t="s" s="11">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D44" s="12">
         <v>1</v>
@@ -3796,7 +3877,7 @@
         <v>19</v>
       </c>
       <c r="C45" t="s" s="11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D45" s="12">
         <v>1</v>
@@ -3805,7 +3886,7 @@
         <v>21</v>
       </c>
       <c r="F45" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
@@ -3815,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s" s="11">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" ht="20.05" customHeight="1">
@@ -3826,7 +3907,7 @@
         <v>12</v>
       </c>
       <c r="C46" t="s" s="11">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D46" s="12">
         <v>1</v>
@@ -3835,7 +3916,7 @@
         <v>14</v>
       </c>
       <c r="F46" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
@@ -3845,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s" s="11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" ht="20.05" customHeight="1">
@@ -3856,7 +3937,7 @@
         <v>12</v>
       </c>
       <c r="C47" t="s" s="11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D47" s="12">
         <v>1</v>
@@ -3865,7 +3946,7 @@
         <v>14</v>
       </c>
       <c r="F47" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
@@ -3875,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s" s="11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" ht="20.05" customHeight="1">
@@ -3886,7 +3967,7 @@
         <v>12</v>
       </c>
       <c r="C48" t="s" s="11">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D48" s="12">
         <v>1</v>
@@ -3895,7 +3976,7 @@
         <v>14</v>
       </c>
       <c r="F48" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
@@ -3905,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s" s="11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" ht="20.05" customHeight="1">
@@ -3916,7 +3997,7 @@
         <v>12</v>
       </c>
       <c r="C49" t="s" s="11">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D49" s="12">
         <v>1</v>
@@ -3925,7 +4006,7 @@
         <v>14</v>
       </c>
       <c r="F49" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
@@ -3935,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s" s="11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" ht="20.05" customHeight="1">
@@ -3946,7 +4027,7 @@
         <v>12</v>
       </c>
       <c r="C50" t="s" s="11">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D50" s="12">
         <v>1</v>
@@ -3955,7 +4036,7 @@
         <v>14</v>
       </c>
       <c r="F50" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G50" s="13"/>
       <c r="H50" s="13"/>
@@ -3965,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s" s="11">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" ht="20.05" customHeight="1">
@@ -3976,7 +4057,7 @@
         <v>12</v>
       </c>
       <c r="C51" t="s" s="11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D51" s="12">
         <v>1</v>
@@ -3985,7 +4066,7 @@
         <v>14</v>
       </c>
       <c r="F51" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
@@ -3995,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s" s="11">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" ht="20.05" customHeight="1">
@@ -4006,7 +4087,7 @@
         <v>12</v>
       </c>
       <c r="C52" t="s" s="11">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D52" s="12">
         <v>1</v>
@@ -4015,7 +4096,7 @@
         <v>14</v>
       </c>
       <c r="F52" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
@@ -4025,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s" s="11">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" ht="20.05" customHeight="1">
@@ -4036,7 +4117,7 @@
         <v>12</v>
       </c>
       <c r="C53" t="s" s="11">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D53" s="12">
         <v>1</v>
@@ -4045,7 +4126,7 @@
         <v>14</v>
       </c>
       <c r="F53" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G53" s="13"/>
       <c r="H53" s="13"/>
@@ -4055,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s" s="11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" ht="20.05" customHeight="1">
@@ -4066,7 +4147,7 @@
         <v>12</v>
       </c>
       <c r="C54" t="s" s="11">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D54" s="12">
         <v>1</v>
@@ -4075,7 +4156,7 @@
         <v>14</v>
       </c>
       <c r="F54" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
@@ -4085,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s" s="11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" ht="20.05" customHeight="1">
@@ -4096,7 +4177,7 @@
         <v>12</v>
       </c>
       <c r="C55" t="s" s="11">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D55" s="12">
         <v>1</v>
@@ -4105,7 +4186,7 @@
         <v>14</v>
       </c>
       <c r="F55" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G55" s="13"/>
       <c r="H55" s="13"/>
@@ -4115,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s" s="11">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" ht="20.05" customHeight="1">
@@ -4126,7 +4207,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="s" s="11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D56" s="12">
         <v>1</v>
@@ -4135,7 +4216,7 @@
         <v>18</v>
       </c>
       <c r="F56" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G56" s="13"/>
       <c r="H56" s="13"/>
@@ -4145,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s" s="11">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" ht="20.05" customHeight="1">
@@ -4156,7 +4237,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="s" s="11">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D57" s="12">
         <v>1</v>
@@ -4165,7 +4246,7 @@
         <v>18</v>
       </c>
       <c r="F57" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G57" s="13"/>
       <c r="H57" s="13"/>
@@ -4175,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s" s="11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" ht="20.05" customHeight="1">
@@ -4186,7 +4267,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="s" s="11">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D58" s="12">
         <v>1</v>
@@ -4195,7 +4276,7 @@
         <v>18</v>
       </c>
       <c r="F58" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
@@ -4205,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s" s="11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" ht="20.05" customHeight="1">
@@ -4216,7 +4297,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="s" s="11">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D59" s="12">
         <v>1</v>
@@ -4225,7 +4306,7 @@
         <v>18</v>
       </c>
       <c r="F59" t="s" s="11">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G59" s="13"/>
       <c r="H59" s="13"/>
@@ -4235,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s" s="11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" ht="20.25" customHeight="1">
@@ -4246,7 +4327,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="s" s="16">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D60" s="17">
         <v>1</v>
@@ -4255,7 +4336,7 @@
         <v>18</v>
       </c>
       <c r="F60" t="s" s="16">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G60" s="18"/>
       <c r="H60" s="18"/>
@@ -4265,14 +4346,14 @@
         <v>0</v>
       </c>
       <c r="K60" t="s" s="16">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" ht="20.25" customHeight="1">
       <c r="A61" s="19"/>
       <c r="B61" s="19"/>
       <c r="C61" t="s" s="20">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D61" s="19"/>
       <c r="E61" s="19"/>
@@ -4282,7 +4363,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="21" cm="1">
         <f t="array" ref="J61">SUM(J3:J60)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61" s="19"/>
     </row>
@@ -4290,6 +4371,10 @@
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="K34" r:id="rId1" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=200009"/>
+    <hyperlink ref="K35" r:id="rId2" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=200009"/>
+  </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
@@ -4315,16 +4400,16 @@
   <sheetData>
     <row r="1" ht="20.25" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B1" t="s" s="3">
         <v>2</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" ht="20.25" customHeight="1">
@@ -4335,10 +4420,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s" s="6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s" s="6">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" ht="20.05" customHeight="1">
@@ -4346,13 +4431,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s" s="11">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
@@ -4360,13 +4445,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s" s="11">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" ht="20.05" customHeight="1">
@@ -4374,13 +4459,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s" s="11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
@@ -4388,13 +4473,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s" s="11">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s" s="11">
         <v>81</v>
-      </c>
-      <c r="D6" t="s" s="11">
-        <v>76</v>
       </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
@@ -4402,13 +4487,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s" s="11">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" ht="20.05" customHeight="1">
@@ -4416,13 +4501,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s" s="11">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
@@ -4430,13 +4515,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s" s="11">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
@@ -4444,13 +4529,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s" s="11">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s" s="11">
-        <v>85</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" ht="20.05" customHeight="1">
@@ -4458,13 +4543,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s" s="11">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s" s="11">
-        <v>85</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
@@ -4472,13 +4557,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="10">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s" s="11">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
@@ -4486,13 +4571,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="10">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s" s="11">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" ht="20.05" customHeight="1">
@@ -4500,13 +4585,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="10">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s" s="11">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" ht="20.05" customHeight="1">
@@ -4514,13 +4599,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="10">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s" s="11">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" ht="20.05" customHeight="1">
@@ -4528,13 +4613,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="10">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s" s="11">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s" s="11">
-        <v>85</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -4548,7 +4633,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:F25"/>
+  <dimension ref="A2:G25"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.10156" style="23" customWidth="1"/>
@@ -4557,105 +4642,116 @@
     <col min="4" max="4" width="61.1719" style="23" customWidth="1"/>
     <col min="5" max="5" width="16.3516" style="23" customWidth="1"/>
     <col min="6" max="6" width="11.7812" style="23" customWidth="1"/>
-    <col min="7" max="16384" width="16.3516" style="23" customWidth="1"/>
+    <col min="7" max="7" width="38.4531" style="23" customWidth="1"/>
+    <col min="8" max="16384" width="16.3516" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" t="s" s="24">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F2" s="25"/>
+      <c r="G2" t="s" s="3">
+        <v>103</v>
+      </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
       <c r="A3" s="26">
         <v>1</v>
       </c>
       <c r="B3" t="s" s="5">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s" s="6">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" t="s" s="6">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F3" t="b" s="7">
         <v>0</v>
       </c>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" ht="20.05" customHeight="1">
       <c r="A4" s="27">
         <v>2</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" t="s" s="11">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" t="b" s="12">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" ht="20.05" customHeight="1">
       <c r="A5" s="27">
         <v>3</v>
       </c>
       <c r="B5" t="s" s="10">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s" s="11">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s" s="11">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" t="b" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="20.05" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="11"/>
+    </row>
+    <row r="6" ht="32.05" customHeight="1">
       <c r="A6" s="27">
         <v>4</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s" s="11">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s" s="11">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" t="b" s="12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G6" t="s" s="11">
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
@@ -4663,53 +4759,58 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s" s="11">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s" s="11">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" t="b" s="12">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
       <c r="A8" s="27">
         <v>6</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s" s="11">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s" s="11">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" t="b" s="12">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" ht="20.05" customHeight="1">
       <c r="A9" s="27">
         <v>7</v>
       </c>
       <c r="B9" t="s" s="10">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s" s="11">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s" s="11">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" t="b" s="12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G9" t="s" s="11">
+        <v>125</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
@@ -4717,223 +4818,235 @@
         <v>8</v>
       </c>
       <c r="B10" t="s" s="10">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s" s="11">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s" s="11">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" t="b" s="12">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" ht="20.05" customHeight="1">
       <c r="A11" s="27">
         <v>9</v>
       </c>
       <c r="B11" t="s" s="10">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s" s="11">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s" s="11">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" t="b" s="12">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" ht="20.05" customHeight="1">
       <c r="A12" s="27">
         <v>10</v>
       </c>
       <c r="B12" t="s" s="10">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s" s="11">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s" s="11">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" t="b" s="12">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" ht="20.05" customHeight="1">
       <c r="A13" s="27">
         <v>11</v>
       </c>
       <c r="B13" t="s" s="10">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" t="s" s="11">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s" s="28">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F13" t="b" s="29">
         <v>0</v>
       </c>
+      <c r="G13" s="30"/>
     </row>
     <row r="14" ht="20.05" customHeight="1">
       <c r="A14" s="27">
         <v>12</v>
       </c>
       <c r="B14" t="s" s="10">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C14" s="13"/>
-      <c r="D14" t="s" s="30">
-        <v>131</v>
-      </c>
-      <c r="E14" t="s" s="31">
-        <v>132</v>
-      </c>
-      <c r="F14" t="b" s="32">
-        <v>0</v>
-      </c>
+      <c r="D14" t="s" s="31">
+        <v>138</v>
+      </c>
+      <c r="E14" t="s" s="32">
+        <v>139</v>
+      </c>
+      <c r="F14" t="b" s="33">
+        <v>0</v>
+      </c>
+      <c r="G14" s="34"/>
     </row>
     <row r="15" ht="20.85" customHeight="1">
       <c r="A15" s="27">
         <v>13</v>
       </c>
       <c r="B15" t="s" s="10">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" t="s" s="11">
-        <v>134</v>
-      </c>
-      <c r="E15" t="s" s="33">
-        <v>135</v>
+        <v>141</v>
+      </c>
+      <c r="E15" t="s" s="35">
+        <v>142</v>
       </c>
       <c r="F15" t="b" s="12">
         <v>0</v>
       </c>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" ht="21.7" customHeight="1">
       <c r="A16" s="27">
         <v>14</v>
       </c>
       <c r="B16" t="s" s="10">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C16" s="13"/>
-      <c r="D16" t="s" s="34">
-        <v>137</v>
-      </c>
-      <c r="E16" t="s" s="35">
-        <v>138</v>
-      </c>
-      <c r="F16" t="b" s="36">
-        <v>0</v>
-      </c>
+      <c r="D16" t="s" s="36">
+        <v>144</v>
+      </c>
+      <c r="E16" t="s" s="37">
+        <v>145</v>
+      </c>
+      <c r="F16" t="b" s="38">
+        <v>0</v>
+      </c>
+      <c r="G16" s="39"/>
     </row>
     <row r="17" ht="20.85" customHeight="1">
       <c r="A17" s="27">
         <v>15</v>
       </c>
       <c r="B17" t="s" s="10">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" t="s" s="11">
-        <v>140</v>
-      </c>
-      <c r="E17" t="s" s="37">
-        <v>141</v>
-      </c>
-      <c r="F17" t="b" s="38">
-        <v>0</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="E17" t="s" s="40">
+        <v>148</v>
+      </c>
+      <c r="F17" t="b" s="41">
+        <v>0</v>
+      </c>
+      <c r="G17" s="42"/>
     </row>
     <row r="18" ht="20.05" customHeight="1">
       <c r="A18" s="27">
         <v>16</v>
       </c>
       <c r="B18" t="s" s="10">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" t="s" s="11">
-        <v>143</v>
-      </c>
-      <c r="E18" t="s" s="39">
-        <v>144</v>
-      </c>
-      <c r="F18" t="b" s="40">
-        <v>0</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E18" t="s" s="43">
+        <v>151</v>
+      </c>
+      <c r="F18" t="b" s="44">
+        <v>0</v>
+      </c>
+      <c r="G18" s="45"/>
     </row>
     <row r="19" ht="20.05" customHeight="1">
       <c r="A19" s="27">
         <v>17</v>
       </c>
       <c r="B19" t="s" s="10">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" t="s" s="11">
-        <v>146</v>
-      </c>
-      <c r="E19" t="s" s="41">
-        <v>147</v>
-      </c>
-      <c r="F19" t="b" s="40">
-        <v>0</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="E19" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="F19" t="b" s="44">
+        <v>0</v>
+      </c>
+      <c r="G19" s="45"/>
     </row>
     <row r="20" ht="20.05" customHeight="1">
       <c r="A20" s="27">
         <v>18</v>
       </c>
       <c r="B20" t="s" s="10">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" t="s" s="11">
-        <v>149</v>
-      </c>
-      <c r="E20" t="s" s="42">
-        <v>150</v>
-      </c>
-      <c r="F20" t="b" s="43">
-        <v>0</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="E20" t="s" s="47">
+        <v>157</v>
+      </c>
+      <c r="F20" t="b" s="48">
+        <v>0</v>
+      </c>
+      <c r="G20" s="49"/>
     </row>
     <row r="21" ht="20.05" customHeight="1">
       <c r="A21" s="27">
         <v>19</v>
       </c>
       <c r="B21" t="s" s="10">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C21" s="13"/>
-      <c r="D21" t="s" s="30">
-        <v>152</v>
-      </c>
-      <c r="E21" t="s" s="44">
-        <v>153</v>
-      </c>
-      <c r="F21" t="b" s="32">
-        <v>0</v>
-      </c>
+      <c r="D21" t="s" s="31">
+        <v>159</v>
+      </c>
+      <c r="E21" t="s" s="50">
+        <v>160</v>
+      </c>
+      <c r="F21" t="b" s="33">
+        <v>0</v>
+      </c>
+      <c r="G21" s="34"/>
     </row>
     <row r="22" ht="20.05" customHeight="1">
       <c r="A22" s="27">
         <v>20</v>
       </c>
       <c r="B22" t="s" s="10">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -4941,50 +5054,54 @@
       <c r="F22" t="b" s="12">
         <v>0</v>
       </c>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" ht="20.05" customHeight="1">
       <c r="A23" s="27">
         <v>21</v>
       </c>
       <c r="B23" t="s" s="10">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" t="s" s="11">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" t="b" s="12">
         <v>0</v>
       </c>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" ht="20.05" customHeight="1">
       <c r="A24" s="27">
         <v>22</v>
       </c>
       <c r="B24" t="s" s="10">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" t="s" s="11">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" t="b" s="12">
         <v>0</v>
       </c>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" ht="20.05" customHeight="1">
-      <c r="A25" s="45"/>
-      <c r="B25" s="46"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
+      <c r="G25" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -5002,17 +5119,17 @@
   <dimension ref="A2:E20"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="47" customWidth="1"/>
-    <col min="2" max="2" width="43.5" style="47" customWidth="1"/>
-    <col min="3" max="3" width="34.2656" style="47" customWidth="1"/>
-    <col min="4" max="4" width="34.5" style="47" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="47" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="47" customWidth="1"/>
+    <col min="1" max="1" width="8.10156" style="53" customWidth="1"/>
+    <col min="2" max="2" width="43.5" style="53" customWidth="1"/>
+    <col min="3" max="3" width="34.2656" style="53" customWidth="1"/>
+    <col min="4" max="4" width="34.5" style="53" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="53" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="53" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5021,19 +5138,19 @@
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" t="s" s="24">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
@@ -5041,14 +5158,14 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="5">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s" s="6">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" t="s" s="6">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
@@ -5056,13 +5173,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s" s="11">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D4" t="s" s="11">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E4" s="13"/>
     </row>
@@ -5071,13 +5188,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="10">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s" s="11">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s" s="11">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E5" s="13"/>
     </row>
@@ -5086,13 +5203,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s" s="11">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s" s="11">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E6" s="13"/>
     </row>
@@ -5101,10 +5218,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s" s="11">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
@@ -5114,14 +5231,14 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" t="s" s="11">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E8" t="s" s="28">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
@@ -5129,14 +5246,14 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="10">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C9" s="13"/>
-      <c r="D9" t="s" s="30">
-        <v>174</v>
-      </c>
-      <c r="E9" t="s" s="31">
-        <v>132</v>
+      <c r="D9" t="s" s="31">
+        <v>181</v>
+      </c>
+      <c r="E9" t="s" s="32">
+        <v>139</v>
       </c>
     </row>
     <row r="10" ht="20.85" customHeight="1">
@@ -5144,14 +5261,14 @@
         <v>8</v>
       </c>
       <c r="B10" t="s" s="10">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" t="s" s="11">
-        <v>175</v>
-      </c>
-      <c r="E10" t="s" s="33">
-        <v>135</v>
+        <v>182</v>
+      </c>
+      <c r="E10" t="s" s="35">
+        <v>142</v>
       </c>
     </row>
     <row r="11" ht="21.7" customHeight="1">
@@ -5159,14 +5276,14 @@
         <v>9</v>
       </c>
       <c r="B11" t="s" s="10">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C11" s="13"/>
-      <c r="D11" t="s" s="34">
-        <v>176</v>
-      </c>
-      <c r="E11" t="s" s="35">
-        <v>138</v>
+      <c r="D11" t="s" s="36">
+        <v>183</v>
+      </c>
+      <c r="E11" t="s" s="37">
+        <v>145</v>
       </c>
     </row>
     <row r="12" ht="20.85" customHeight="1">
@@ -5174,14 +5291,14 @@
         <v>10</v>
       </c>
       <c r="B12" t="s" s="10">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" t="s" s="11">
-        <v>177</v>
-      </c>
-      <c r="E12" t="s" s="37">
-        <v>141</v>
+        <v>184</v>
+      </c>
+      <c r="E12" t="s" s="40">
+        <v>148</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
@@ -5189,14 +5306,14 @@
         <v>11</v>
       </c>
       <c r="B13" t="s" s="10">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" t="s" s="11">
-        <v>178</v>
-      </c>
-      <c r="E13" t="s" s="39">
-        <v>144</v>
+        <v>185</v>
+      </c>
+      <c r="E13" t="s" s="43">
+        <v>151</v>
       </c>
     </row>
     <row r="14" ht="20.05" customHeight="1">
@@ -5204,14 +5321,14 @@
         <v>12</v>
       </c>
       <c r="B14" t="s" s="10">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" t="s" s="11">
-        <v>179</v>
-      </c>
-      <c r="E14" t="s" s="41">
-        <v>147</v>
+        <v>186</v>
+      </c>
+      <c r="E14" t="s" s="46">
+        <v>154</v>
       </c>
     </row>
     <row r="15" ht="20.05" customHeight="1">
@@ -5219,14 +5336,14 @@
         <v>13</v>
       </c>
       <c r="B15" t="s" s="10">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" t="s" s="11">
-        <v>180</v>
-      </c>
-      <c r="E15" t="s" s="42">
-        <v>150</v>
+        <v>187</v>
+      </c>
+      <c r="E15" t="s" s="47">
+        <v>157</v>
       </c>
     </row>
     <row r="16" ht="20.05" customHeight="1">
@@ -5234,14 +5351,14 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="10">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C16" s="13"/>
-      <c r="D16" t="s" s="30">
-        <v>181</v>
-      </c>
-      <c r="E16" t="s" s="44">
-        <v>153</v>
+      <c r="D16" t="s" s="31">
+        <v>188</v>
+      </c>
+      <c r="E16" t="s" s="50">
+        <v>160</v>
       </c>
     </row>
     <row r="17" ht="20.05" customHeight="1">
@@ -5249,13 +5366,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s" s="10">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s" s="11">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D17" t="s" s="11">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E17" s="13"/>
     </row>
@@ -5264,22 +5381,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="s" s="10">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
     </row>
     <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="45"/>
-      <c r="B19" s="46"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="52"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
     </row>
     <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="45"/>
-      <c r="B20" s="46"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="52"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -5304,17 +5421,17 @@
   <dimension ref="A2:E9"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="48" customWidth="1"/>
-    <col min="2" max="2" width="54.8516" style="48" customWidth="1"/>
-    <col min="3" max="3" width="23.6719" style="48" customWidth="1"/>
-    <col min="4" max="4" width="26.3516" style="48" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="48" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="48" customWidth="1"/>
+    <col min="1" max="1" width="8.10156" style="54" customWidth="1"/>
+    <col min="2" max="2" width="54.8516" style="54" customWidth="1"/>
+    <col min="3" max="3" width="23.6719" style="54" customWidth="1"/>
+    <col min="4" max="4" width="26.3516" style="54" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="54" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5323,19 +5440,19 @@
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" t="s" s="24">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
@@ -5343,14 +5460,14 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="5">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s" s="6">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" t="s" s="6">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
@@ -5358,11 +5475,11 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" t="s" s="11">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E4" s="13"/>
     </row>
@@ -5371,13 +5488,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="10">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C5" t="s" s="11">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D5" t="s" s="11">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E5" s="13"/>
     </row>
@@ -5386,13 +5503,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s" s="11">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D6" t="s" s="11">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E6" s="13"/>
     </row>
@@ -5401,14 +5518,14 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" t="s" s="11">
-        <v>196</v>
-      </c>
-      <c r="E7" t="s" s="49">
-        <v>144</v>
+        <v>203</v>
+      </c>
+      <c r="E7" t="s" s="55">
+        <v>151</v>
       </c>
     </row>
     <row r="8" ht="20.05" customHeight="1">
@@ -5416,14 +5533,14 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" t="s" s="11">
-        <v>198</v>
-      </c>
-      <c r="E8" t="s" s="50">
-        <v>141</v>
+        <v>205</v>
+      </c>
+      <c r="E8" t="s" s="56">
+        <v>148</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
@@ -5431,7 +5548,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="10">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -5457,17 +5574,17 @@
   <dimension ref="A2:E18"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="51" customWidth="1"/>
-    <col min="2" max="2" width="56.1172" style="51" customWidth="1"/>
-    <col min="3" max="3" width="23.6719" style="51" customWidth="1"/>
-    <col min="4" max="4" width="47.2422" style="51" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="51" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="51" customWidth="1"/>
+    <col min="1" max="1" width="8.10156" style="57" customWidth="1"/>
+    <col min="2" max="2" width="56.1172" style="57" customWidth="1"/>
+    <col min="3" max="3" width="23.6719" style="57" customWidth="1"/>
+    <col min="4" max="4" width="47.2422" style="57" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="57" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5476,19 +5593,19 @@
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" t="s" s="24">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
@@ -5496,14 +5613,14 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="5">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s" s="6">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" t="s" s="6">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
@@ -5511,11 +5628,11 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" t="s" s="11">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E4" s="13"/>
     </row>
@@ -5524,13 +5641,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="10">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s" s="11">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D5" t="s" s="11">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E5" s="13"/>
     </row>
@@ -5539,10 +5656,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C6" t="s" s="11">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
@@ -5552,11 +5669,11 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" t="s" s="11">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E7" s="13"/>
     </row>
@@ -5565,7 +5682,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -5576,13 +5693,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="10">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C9" t="s" s="11">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D9" t="s" s="11">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E9" s="13"/>
     </row>
@@ -5591,29 +5708,29 @@
         <v>8</v>
       </c>
       <c r="B10" t="s" s="10">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C10" t="s" s="11">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D10" t="s" s="11">
-        <v>214</v>
-      </c>
-      <c r="E10" s="52"/>
+        <v>221</v>
+      </c>
+      <c r="E10" s="58"/>
     </row>
     <row r="11" ht="20.05" customHeight="1">
       <c r="A11" s="27">
         <v>9</v>
       </c>
       <c r="B11" t="s" s="10">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" t="s" s="11">
-        <v>216</v>
-      </c>
-      <c r="E11" t="s" s="50">
-        <v>141</v>
+        <v>223</v>
+      </c>
+      <c r="E11" t="s" s="56">
+        <v>148</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
@@ -5621,14 +5738,14 @@
         <v>10</v>
       </c>
       <c r="B12" t="s" s="10">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" t="s" s="11">
-        <v>217</v>
-      </c>
-      <c r="E12" t="s" s="39">
-        <v>144</v>
+        <v>224</v>
+      </c>
+      <c r="E12" t="s" s="43">
+        <v>151</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
@@ -5636,14 +5753,14 @@
         <v>11</v>
       </c>
       <c r="B13" t="s" s="10">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" t="s" s="11">
-        <v>218</v>
-      </c>
-      <c r="E13" t="s" s="41">
-        <v>147</v>
+        <v>225</v>
+      </c>
+      <c r="E13" t="s" s="46">
+        <v>154</v>
       </c>
     </row>
     <row r="14" ht="20.05" customHeight="1">
@@ -5651,14 +5768,14 @@
         <v>12</v>
       </c>
       <c r="B14" t="s" s="10">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" t="s" s="11">
-        <v>219</v>
-      </c>
-      <c r="E14" t="s" s="42">
-        <v>150</v>
+        <v>226</v>
+      </c>
+      <c r="E14" t="s" s="47">
+        <v>157</v>
       </c>
     </row>
     <row r="15" ht="20.05" customHeight="1">
@@ -5666,14 +5783,14 @@
         <v>13</v>
       </c>
       <c r="B15" t="s" s="10">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C15" s="13"/>
-      <c r="D15" t="s" s="30">
-        <v>220</v>
-      </c>
-      <c r="E15" t="s" s="44">
-        <v>153</v>
+      <c r="D15" t="s" s="31">
+        <v>227</v>
+      </c>
+      <c r="E15" t="s" s="50">
+        <v>160</v>
       </c>
     </row>
     <row r="16" ht="20.05" customHeight="1">
@@ -5681,22 +5798,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="10">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
     </row>
     <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="45"/>
-      <c r="B17" s="46"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="52"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
     </row>
     <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="45"/>
-      <c r="B18" s="46"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="52"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -5721,10 +5838,10 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.3516" style="53" customWidth="1"/>
-    <col min="2" max="2" width="35.1484" style="53" customWidth="1"/>
-    <col min="3" max="5" width="16.3516" style="53" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="53" customWidth="1"/>
+    <col min="1" max="1" width="16.3516" style="59" customWidth="1"/>
+    <col min="2" max="2" width="35.1484" style="59" customWidth="1"/>
+    <col min="3" max="5" width="16.3516" style="59" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="59" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1">
@@ -5735,70 +5852,70 @@
       <c r="E1" s="25"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="54"/>
+      <c r="A2" s="60"/>
       <c r="B2" t="s" s="5">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
     </row>
     <row r="3" ht="32.05" customHeight="1">
-      <c r="A3" s="55"/>
+      <c r="A3" s="61"/>
       <c r="B3" t="s" s="10">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
     </row>
     <row r="4" ht="32.05" customHeight="1">
-      <c r="A4" s="55"/>
+      <c r="A4" s="61"/>
       <c r="B4" t="s" s="10">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
     </row>
     <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" s="55"/>
-      <c r="B5" s="46"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="55"/>
-      <c r="B6" s="46"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="52"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="55"/>
-      <c r="B7" s="46"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="55"/>
-      <c r="B8" s="46"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="52"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="55"/>
-      <c r="B9" s="46"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
     </row>
     <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="55"/>
-      <c r="B10" s="46"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="52"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -5820,17 +5937,17 @@
   <dimension ref="A2:E20"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="56" customWidth="1"/>
-    <col min="2" max="2" width="57.1719" style="56" customWidth="1"/>
-    <col min="3" max="3" width="33.8125" style="56" customWidth="1"/>
-    <col min="4" max="4" width="35.0781" style="56" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="56" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="56" customWidth="1"/>
+    <col min="1" max="1" width="8.10156" style="62" customWidth="1"/>
+    <col min="2" max="2" width="57.1719" style="62" customWidth="1"/>
+    <col min="3" max="3" width="33.8125" style="62" customWidth="1"/>
+    <col min="4" max="4" width="35.0781" style="62" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="62" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="62" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5839,19 +5956,19 @@
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" t="s" s="24">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
@@ -5859,14 +5976,14 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="5">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s" s="6">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" t="s" s="6">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
@@ -5874,11 +5991,11 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" t="s" s="11">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E4" s="13"/>
     </row>
@@ -5887,7 +6004,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="10">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -5898,11 +6015,11 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" t="s" s="11">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E6" s="13"/>
     </row>
@@ -5911,13 +6028,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s" s="11">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s" s="11">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E7" s="13"/>
     </row>
@@ -5926,16 +6043,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C8" t="s" s="11">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D8" t="s" s="11">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E8" t="s" s="28">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
@@ -5943,16 +6060,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="10">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s" s="11">
-        <v>230</v>
-      </c>
-      <c r="D9" t="s" s="30">
-        <v>232</v>
-      </c>
-      <c r="E9" t="s" s="31">
-        <v>132</v>
+        <v>237</v>
+      </c>
+      <c r="D9" t="s" s="31">
+        <v>239</v>
+      </c>
+      <c r="E9" t="s" s="32">
+        <v>139</v>
       </c>
     </row>
     <row r="10" ht="20.85" customHeight="1">
@@ -5960,16 +6077,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s" s="10">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s" s="11">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D10" t="s" s="11">
-        <v>233</v>
-      </c>
-      <c r="E10" t="s" s="33">
-        <v>135</v>
+        <v>240</v>
+      </c>
+      <c r="E10" t="s" s="35">
+        <v>142</v>
       </c>
     </row>
     <row r="11" ht="21.7" customHeight="1">
@@ -5977,16 +6094,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s" s="10">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C11" t="s" s="11">
-        <v>230</v>
-      </c>
-      <c r="D11" t="s" s="34">
-        <v>234</v>
-      </c>
-      <c r="E11" t="s" s="35">
-        <v>138</v>
+        <v>237</v>
+      </c>
+      <c r="D11" t="s" s="36">
+        <v>241</v>
+      </c>
+      <c r="E11" t="s" s="37">
+        <v>145</v>
       </c>
     </row>
     <row r="12" ht="20.85" customHeight="1">
@@ -5994,16 +6111,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s" s="10">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s" s="11">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D12" t="s" s="11">
-        <v>235</v>
-      </c>
-      <c r="E12" t="s" s="37">
-        <v>141</v>
+        <v>242</v>
+      </c>
+      <c r="E12" t="s" s="40">
+        <v>148</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
@@ -6011,16 +6128,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s" s="10">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C13" t="s" s="11">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D13" t="s" s="11">
-        <v>236</v>
-      </c>
-      <c r="E13" t="s" s="39">
-        <v>144</v>
+        <v>243</v>
+      </c>
+      <c r="E13" t="s" s="43">
+        <v>151</v>
       </c>
     </row>
     <row r="14" ht="20.05" customHeight="1">
@@ -6028,16 +6145,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s" s="10">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s" s="11">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D14" t="s" s="11">
-        <v>237</v>
-      </c>
-      <c r="E14" t="s" s="41">
-        <v>147</v>
+        <v>244</v>
+      </c>
+      <c r="E14" t="s" s="46">
+        <v>154</v>
       </c>
     </row>
     <row r="15" ht="20.05" customHeight="1">
@@ -6045,16 +6162,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s" s="10">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C15" t="s" s="11">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D15" t="s" s="11">
-        <v>238</v>
-      </c>
-      <c r="E15" t="s" s="57">
-        <v>150</v>
+        <v>245</v>
+      </c>
+      <c r="E15" t="s" s="63">
+        <v>157</v>
       </c>
     </row>
     <row r="16" ht="20.05" customHeight="1">
@@ -6062,7 +6179,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="10">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
@@ -6073,11 +6190,11 @@
         <v>15</v>
       </c>
       <c r="B17" t="s" s="10">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" t="s" s="11">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E17" s="13"/>
     </row>
@@ -6086,22 +6203,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="s" s="10">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
     </row>
     <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="45"/>
-      <c r="B19" s="46"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="52"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
     </row>
     <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="45"/>
-      <c r="B20" s="46"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="52"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -6126,17 +6243,17 @@
   <dimension ref="A2:E15"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="58" customWidth="1"/>
-    <col min="2" max="2" width="32.6719" style="58" customWidth="1"/>
-    <col min="3" max="3" width="23.6719" style="58" customWidth="1"/>
-    <col min="4" max="4" width="24.625" style="58" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="58" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="58" customWidth="1"/>
+    <col min="1" max="1" width="8.10156" style="64" customWidth="1"/>
+    <col min="2" max="2" width="32.6719" style="64" customWidth="1"/>
+    <col min="3" max="3" width="23.6719" style="64" customWidth="1"/>
+    <col min="4" max="4" width="24.625" style="64" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="64" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="64" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6145,19 +6262,19 @@
     </row>
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" t="s" s="24">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
@@ -6165,14 +6282,14 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="5">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s" s="6">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" t="s" s="6">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
@@ -6180,11 +6297,11 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" t="s" s="11">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E4" s="13"/>
     </row>
@@ -6193,13 +6310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="10">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s" s="11">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D5" t="s" s="11">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E5" s="13"/>
     </row>
@@ -6208,7 +6325,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -6219,11 +6336,11 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" t="s" s="11">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E7" s="13"/>
     </row>
@@ -6232,11 +6349,11 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" t="s" s="11">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E8" s="13"/>
     </row>
@@ -6245,11 +6362,11 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="10">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" t="s" s="11">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="E9" s="13"/>
     </row>
@@ -6258,14 +6375,14 @@
         <v>8</v>
       </c>
       <c r="B10" t="s" s="10">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" t="s" s="11">
-        <v>255</v>
-      </c>
-      <c r="E10" t="s" s="39">
-        <v>144</v>
+        <v>262</v>
+      </c>
+      <c r="E10" t="s" s="43">
+        <v>151</v>
       </c>
     </row>
     <row r="11" ht="20.05" customHeight="1">
@@ -6273,16 +6390,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s" s="10">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s" s="11">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s" s="11">
-        <v>257</v>
-      </c>
-      <c r="E11" t="s" s="41">
-        <v>147</v>
+        <v>264</v>
+      </c>
+      <c r="E11" t="s" s="46">
+        <v>154</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
@@ -6290,16 +6407,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s" s="10">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C12" t="s" s="11">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s" s="11">
-        <v>259</v>
-      </c>
-      <c r="E12" t="s" s="57">
-        <v>150</v>
+        <v>266</v>
+      </c>
+      <c r="E12" t="s" s="63">
+        <v>157</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
@@ -6307,22 +6424,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s" s="10">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
     </row>
     <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="45"/>
-      <c r="B14" s="46"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="52"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
     </row>
     <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="45"/>
-      <c r="B15" s="46"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="52"/>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>

--- a/STELLA-1.2/lab_spec_documents/Lab Spec Build Instructions.xlsx
+++ b/STELLA-1.2/lab_spec_documents/Lab Spec Build Instructions.xlsx
@@ -7,13 +7,16 @@
   <sheets>
     <sheet name="Parts" sheetId="1" r:id="rId5"/>
     <sheet name="Drawings" sheetId="2" r:id="rId6"/>
-    <sheet name="main board" sheetId="3" r:id="rId7"/>
-    <sheet name="cuvette cantilever board" sheetId="4" r:id="rId8"/>
-    <sheet name="cuvette drop board" sheetId="5" r:id="rId9"/>
-    <sheet name="cuvette excitation board" sheetId="6" r:id="rId10"/>
-    <sheet name="cuvette join drop + excitation" sheetId="7" r:id="rId11"/>
-    <sheet name="pcr tube cantilever board" sheetId="8" r:id="rId12"/>
-    <sheet name="pcr tube excitation board" sheetId="9" r:id="rId13"/>
+    <sheet name="smt-LED" sheetId="3" r:id="rId7"/>
+    <sheet name="main board" sheetId="4" r:id="rId8"/>
+    <sheet name="cuvette cantilever board" sheetId="5" r:id="rId9"/>
+    <sheet name="cuvette drop board" sheetId="6" r:id="rId10"/>
+    <sheet name="cuvette excitation board" sheetId="7" r:id="rId11"/>
+    <sheet name="cuvette join drop + excitation" sheetId="8" r:id="rId12"/>
+    <sheet name="pcr tube cantilever board" sheetId="9" r:id="rId13"/>
+    <sheet name="pcr tube excitation board" sheetId="10" r:id="rId14"/>
+    <sheet name="Calculations" sheetId="11" r:id="rId15"/>
+    <sheet name="software tests" sheetId="12" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="421">
   <si>
     <t>STELLA Lab Spec parts</t>
   </si>
@@ -91,229 +94,155 @@
     <t>LS</t>
   </si>
   <si>
+    <t>Adafruit half size proto board</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Adafruit</t>
+  </si>
+  <si>
+    <t>Magnet coupler 4 pins</t>
+  </si>
+  <si>
+    <t>Magnet coupler 3 pins</t>
+  </si>
+  <si>
     <t>Adafruit ADS1015 quad 12 bit ADC</t>
   </si>
   <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>Electronics</t>
-  </si>
-  <si>
-    <t>Adafruit</t>
+    <t>Adafruit MCP4728 quad 12 bit DAC</t>
+  </si>
+  <si>
+    <t>Socket headers, 6 pos</t>
+  </si>
+  <si>
+    <t>Digikey</t>
+  </si>
+  <si>
+    <t>4627-FH254V-06-6TBKG98</t>
+  </si>
+  <si>
+    <t>PN2222ABU transistor</t>
+  </si>
+  <si>
+    <t>PN2222AFS-ND</t>
+  </si>
+  <si>
+    <t>1Ω 1% 1/4W resistor</t>
+  </si>
+  <si>
+    <t>13-MF0207FRE52-1RTR</t>
+  </si>
+  <si>
+    <t>100kΩ resistor</t>
+  </si>
+  <si>
+    <t>RNF14FTD100K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50Ω resistor </t>
+  </si>
+  <si>
+    <t>RNF14FTD49R9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Socket header 3x3 pos </t>
+  </si>
+  <si>
+    <t>SSW-103-01-G-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Socket header 3x2 pos </t>
+  </si>
+  <si>
+    <t>SAM12901-ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Socket header 3x1 pos </t>
+  </si>
+  <si>
+    <t>SAM11930-ND</t>
+  </si>
+  <si>
+    <t>LS housing base</t>
+  </si>
+  <si>
+    <t>Print</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>3d print part</t>
+  </si>
+  <si>
+    <t>0.2mm layers</t>
+  </si>
+  <si>
+    <t>Cuvette</t>
+  </si>
+  <si>
+    <t>Cuvette config</t>
+  </si>
+  <si>
+    <t>Consumables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Scientific </t>
+  </si>
+  <si>
+    <t>1180W05</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>https://www.thomassci.com/p/spectrophotometer-cuvettes?q=1180W05</t>
+    </r>
+  </si>
+  <si>
+    <t>$30 for 100 pcs</t>
+  </si>
+  <si>
+    <t>Sparkfun mini proto board</t>
+  </si>
+  <si>
+    <t>PRT-12702</t>
+  </si>
+  <si>
+    <t>Proto-Advantage small proto board</t>
+  </si>
+  <si>
+    <t>Proto-Advantage</t>
+  </si>
+  <si>
+    <t>SBB1002-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>https://www.proto-advantage.com/store/product_info.php?products_id=200009</t>
+    </r>
   </si>
   <si>
     <t>Adafruit AS7341 spectral sensor</t>
   </si>
   <si>
-    <t>Cuvette config</t>
-  </si>
-  <si>
-    <t>PCR tube config</t>
-  </si>
-  <si>
-    <t>Adafruit half size proto board</t>
-  </si>
-  <si>
-    <t>Adafruit MCP4728 quad 12 bit DAC</t>
-  </si>
-  <si>
-    <t>Magnet coupler 3 pins</t>
-  </si>
-  <si>
-    <t>Magnet coupler 4 pins</t>
-  </si>
-  <si>
-    <t>White LED panel</t>
-  </si>
-  <si>
-    <t>Pin header 3 pos</t>
-  </si>
-  <si>
-    <t>PN 392 order only one package at $5 for all lines with this part number</t>
-  </si>
-  <si>
-    <t>Pin header 6 pos</t>
-  </si>
-  <si>
-    <t>Pin header RA 6 pos</t>
-  </si>
-  <si>
-    <t>PN 1540 order only one package at $6 for all lines with this part number</t>
-  </si>
-  <si>
-    <t>Pin header single</t>
-  </si>
-  <si>
-    <t>100kΩ resistor</t>
-  </si>
-  <si>
-    <t>Digikey</t>
-  </si>
-  <si>
-    <t>RNF14FTD100K</t>
-  </si>
-  <si>
-    <t>1Ω 1% 1/4W resistor</t>
-  </si>
-  <si>
-    <t>13-MF0207FRE52-1RTR</t>
-  </si>
-  <si>
-    <t>365nm LED 3mm</t>
-  </si>
-  <si>
-    <t>1125-MTE3660C5-UV-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50Ω resistor </t>
-  </si>
-  <si>
-    <t>RNF14FTD49R9</t>
-  </si>
-  <si>
-    <t>640nm LED 3mm</t>
-  </si>
-  <si>
-    <t>MTE7063C2-UR</t>
-  </si>
-  <si>
-    <t>PN2222ABU transistor</t>
-  </si>
-  <si>
-    <t>PN2222AFS-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Socket header 3x1 pos </t>
-  </si>
-  <si>
-    <t>SAM11930-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Socket header 3x2 pos </t>
-  </si>
-  <si>
-    <t>SAM12901-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Socket header 3x3 pos </t>
-  </si>
-  <si>
-    <t>SSW-103-01-G-T</t>
-  </si>
-  <si>
-    <t>Socket header 6 pos</t>
-  </si>
-  <si>
-    <t>4627-FH254V-06-6TBKG98</t>
-  </si>
-  <si>
-    <t>Socket header, RA, 6 pos</t>
-  </si>
-  <si>
-    <t>S5481-ND</t>
-  </si>
-  <si>
-    <t>Socket headers, 6 pos</t>
-  </si>
-  <si>
-    <t>Sparkfun mini proto board</t>
-  </si>
-  <si>
-    <t>PRT-12702</t>
-  </si>
-  <si>
-    <t>Pin header 3x2 pos</t>
-  </si>
-  <si>
-    <t>67997-206HLF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">488nm LED smt </t>
-  </si>
-  <si>
-    <t>Mouser</t>
-  </si>
-  <si>
-    <t>720-GCVL113KQKSV2V30</t>
-  </si>
-  <si>
-    <t>720-GCVL113KQKSV2V31</t>
-  </si>
-  <si>
-    <t>LS housing base</t>
-  </si>
-  <si>
-    <t>Print</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>3d print part</t>
-  </si>
-  <si>
-    <t>0.2mm layers</t>
-  </si>
-  <si>
-    <t>LS-C2 blackout shutter</t>
-  </si>
-  <si>
-    <t>0.1mm layers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LS-C2 cuvette block </t>
-  </si>
-  <si>
-    <t>LS-C2 cuvette block foot pair, 2up</t>
-  </si>
-  <si>
-    <t>LS-C2 cuvette pedestal</t>
-  </si>
-  <si>
-    <t>LS-C2 detector block</t>
-  </si>
-  <si>
-    <t>0.1mm layers — add support to center bridge</t>
-  </si>
-  <si>
-    <t>LS-C2 detector block assembly fixture</t>
-  </si>
-  <si>
-    <t>LS-C2 end cover</t>
-  </si>
-  <si>
-    <t>LS-C2 side LED cover, flag</t>
-  </si>
-  <si>
-    <t>LS-C2 side LED cover, plain</t>
-  </si>
-  <si>
-    <t>LS-C2 swing lid</t>
-  </si>
-  <si>
-    <t>LS-P2 end cover</t>
-  </si>
-  <si>
-    <t>LS-P2 hinge pin</t>
-  </si>
-  <si>
-    <t>LS-P2 sensor retainer</t>
-  </si>
-  <si>
-    <t>LS-P2 swing door</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LS-P2 test position (single or triple source) </t>
-  </si>
-  <si>
-    <t>0.1mm layers — Add supports to main overhang, organic style seems to be easier to remove</t>
-  </si>
-  <si>
     <t>Proto-Advantage LED2 - DIP adapter</t>
-  </si>
-  <si>
-    <t>Proto-Advantage</t>
   </si>
   <si>
     <t>IPC0224</t>
@@ -330,10 +259,25 @@
     </r>
   </si>
   <si>
-    <t>Proto-Advantage small proto board</t>
-  </si>
-  <si>
-    <t>SBB1002-1</t>
+    <t>365nm LED 3mm</t>
+  </si>
+  <si>
+    <t>1125-MTE3660C5-UV-ND</t>
+  </si>
+  <si>
+    <t>640nm LED 3mm</t>
+  </si>
+  <si>
+    <t>MTE7063C2-UR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488nm LED smt </t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>GC VJLPL1.13-KQKS-V2V3-1</t>
   </si>
   <si>
     <r>
@@ -343,37 +287,77 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://www.proto-advantage.com/store/product_info.php?products_id=200009</t>
+      <t>https://www.mouser.com/ProductDetail/ams-OSRAM/GC-VJLPL1.13-KQKS-V2V3-1?qs=QpmGXVUTftHD6Ze6bLOUKg==</t>
     </r>
   </si>
   <si>
-    <t>Cuvette</t>
-  </si>
-  <si>
-    <t>Consumables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Scientific </t>
-  </si>
-  <si>
-    <t>1180W05</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-      </rPr>
-      <t>https://www.thomassci.com/p/spectrophotometer-cuvettes?q=1180W05</t>
-    </r>
-  </si>
-  <si>
-    <t>$30 for 100 pcs</t>
+    <t>Pin header 3x2 pos</t>
+  </si>
+  <si>
+    <t>67997-206HLF</t>
+  </si>
+  <si>
+    <t>Pin header 3 pos</t>
+  </si>
+  <si>
+    <t>PN 392 order only one package at $5 for all lines with this part number</t>
+  </si>
+  <si>
+    <t>Pin header single</t>
+  </si>
+  <si>
+    <t>Socket header 6 pos</t>
+  </si>
+  <si>
+    <t>Pin header RA 6 pos</t>
+  </si>
+  <si>
+    <t>PN 1540 order only one package at $6 for all lines with this part number</t>
+  </si>
+  <si>
+    <t>White LED panel</t>
+  </si>
+  <si>
+    <t>LS-C2 end cover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LS-C2 cuvette block </t>
+  </si>
+  <si>
+    <t>0.1mm layers</t>
+  </si>
+  <si>
+    <t>LS-C2 cuvette block foot pair, 2up</t>
+  </si>
+  <si>
+    <t>LS-C2 blackout shutter</t>
+  </si>
+  <si>
+    <t>LS-C2 side LED cover, plain</t>
+  </si>
+  <si>
+    <t>LS-C2 side LED cover, flag</t>
+  </si>
+  <si>
+    <t>LS-C2 cuvette pedestal</t>
+  </si>
+  <si>
+    <t>LS-C2 detector block</t>
+  </si>
+  <si>
+    <t>0.1mm layers — add support to center bridge</t>
+  </si>
+  <si>
+    <t>LS-C2 detector block assembly fixture</t>
+  </si>
+  <si>
+    <t>LS-C2 swing lid</t>
   </si>
   <si>
     <t>PCR 0.2mL tube</t>
+  </si>
+  <si>
+    <t>PCR tube config</t>
   </si>
   <si>
     <t>Fisher Scientific</t>
@@ -404,6 +388,36 @@
     <t>$33 for 1000 pcs</t>
   </si>
   <si>
+    <t>Pin header 6 pos</t>
+  </si>
+  <si>
+    <t>Socket header, RA, 6 pos</t>
+  </si>
+  <si>
+    <t>S5481-ND</t>
+  </si>
+  <si>
+    <t>720-GCVL113KQKSV2V31</t>
+  </si>
+  <si>
+    <t>LS-P2 end cover</t>
+  </si>
+  <si>
+    <t>LS-P2 swing door</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LS-P2 test position (single or triple source) </t>
+  </si>
+  <si>
+    <t>0.1mm layers — Add supports to main overhang, organic style seems to be easier to remove</t>
+  </si>
+  <si>
+    <t>LS-P2 sensor retainer</t>
+  </si>
+  <si>
+    <t>LS-P2 hinge pin</t>
+  </si>
+  <si>
     <t>Column cost</t>
   </si>
   <si>
@@ -482,12 +496,116 @@
     <t>LS-P2 Assembly drawing</t>
   </si>
   <si>
+    <t>surface mount technology LED adapter board build</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">print fixtures </t>
+  </si>
+  <si>
+    <t>clean adapter board and stencil w isopropanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identify and mark LED (-) </t>
+  </si>
+  <si>
+    <t>insert adapter board in stencil fixture per diagram</t>
+  </si>
+  <si>
+    <t>insert stencil in stencil fixture per diagram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extrude a small amount of solder paste across the ends of the stencil slots, like the upper cross bar on a π symbol. </t>
+  </si>
+  <si>
+    <t>use the squeegee to fill the stencil slots with solder paste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carefully remove the stencil without disturbing the = made by the soldier paste. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">use fine tweezers to orient the LED correctly: The dot you make in 3 should point to the pin 1 side of the board, where there is a little white dot to match. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">place the LED on the solder paste =. It doesn’t have to be exactly aligned, the surface tension will pull it into alignment when the solder is molten. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">heat the hotplate to TBDºC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">BE VERY CAUTIOUS, it’s a very hot stove. Don’t let any part of your hand make contact with the hot surface. </t>
+    </r>
+  </si>
+  <si>
+    <t>carefully extract the board, with the LED balanced on the solder paste, from the stencil fixture</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">…heat, watch for melt </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>CAREFULLY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">…remove from heat. allow to cool. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">…probe w meter set to diode mode to check polarity. </t>
+  </si>
+  <si>
+    <t>if incorrect, install backwards on excitation board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…set board, diode down, in the pin alignment fixture </t>
+  </si>
+  <si>
+    <t xml:space="preserve">… set pins on board, using pin alignment board… </t>
+  </si>
+  <si>
+    <t>… solder outer pins</t>
+  </si>
+  <si>
+    <t>… remove alignment board</t>
+  </si>
+  <si>
+    <t>… solder inner pins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">… check polarity again. </t>
+  </si>
+  <si>
+    <t>… install on excitation board</t>
+  </si>
+  <si>
     <t>STELLA Lab Spec Main Board</t>
   </si>
   <si>
-    <t>Step</t>
-  </si>
-  <si>
     <t>Action</t>
   </si>
   <si>
@@ -692,6 +810,9 @@
     <t>STELLA Lab Spec Cuvette Cantilever Board</t>
   </si>
   <si>
+    <t>Done</t>
+  </si>
+  <si>
     <t>Sparkfun mini</t>
   </si>
   <si>
@@ -701,204 +822,201 @@
     <t>Using main board as a template, install pin headers</t>
   </si>
   <si>
+    <t>3x2 one place, 3 pos one place, 1 pos six places</t>
+  </si>
+  <si>
+    <t>1-2ABC, A4, B5, C6, C13, B14, A16, 17ABC</t>
+  </si>
+  <si>
+    <t>Fixture detector board at right angles to cantilever board</t>
+  </si>
+  <si>
+    <t>6 pos right angle pin header</t>
+  </si>
+  <si>
+    <t>G7-12</t>
+  </si>
+  <si>
+    <t>Install socket header for drop board</t>
+  </si>
+  <si>
+    <t>6 pos socket header</t>
+  </si>
+  <si>
+    <t>G1-6</t>
+  </si>
+  <si>
+    <t>Note: flatten the wiring along row F to clear the drop board</t>
+  </si>
+  <si>
+    <t>Wires can stick up between D, E and F</t>
+  </si>
+  <si>
+    <t>E2-F11</t>
+  </si>
+  <si>
+    <t>E1-F12</t>
+  </si>
+  <si>
+    <t>E15-F10</t>
+  </si>
+  <si>
+    <t>E17-F9</t>
+  </si>
+  <si>
+    <t>E14-F6</t>
+  </si>
+  <si>
+    <t>E13-F5</t>
+  </si>
+  <si>
+    <t>E6-F4</t>
+  </si>
+  <si>
+    <t>E5-F3</t>
+  </si>
+  <si>
+    <t>E4-F2</t>
+  </si>
+  <si>
+    <t>Test fit the drop board</t>
+  </si>
+  <si>
+    <t>STELLA Lab Spec Cuvette Drop Board</t>
+  </si>
+  <si>
+    <t>Proto-Advantage 1.1x1.7”</t>
+  </si>
+  <si>
+    <t>Epoxy color</t>
+  </si>
+  <si>
+    <t>F1-2, F2-3, F3-4, F4-5, F5-6 F6-7</t>
+  </si>
+  <si>
+    <t>install right angle pin headers, long pins towards the edges of the board</t>
+  </si>
+  <si>
+    <t>6 pos, two places</t>
+  </si>
+  <si>
+    <t>B1-6, G1-6</t>
+  </si>
+  <si>
+    <t>Install current limit resistors, short to G pins on header</t>
+  </si>
+  <si>
+    <t>50Ω, three places</t>
+  </si>
+  <si>
+    <t>FG2-C2, FG3-C3, FG4-C4</t>
+  </si>
+  <si>
+    <t>Install channel 0 wires, short to G pin on header</t>
+  </si>
+  <si>
+    <t>FG5-C5</t>
+  </si>
+  <si>
+    <t>Install 5V wire, short to G pin on header</t>
+  </si>
+  <si>
+    <t>FG6-C6</t>
+  </si>
+  <si>
+    <t>STELLA Lab Spec Cuvette Excitation Board</t>
+  </si>
+  <si>
+    <t>F1-G1, F16-G16</t>
+  </si>
+  <si>
+    <t>Install bottom LED, smt</t>
+  </si>
+  <si>
+    <t>488nm</t>
+  </si>
+  <si>
+    <t>(+) FG10, (dot) FG7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trim backlight LED panel (score with knife and snap) </t>
+  </si>
+  <si>
+    <t>Shorten the panel by 15mm</t>
+  </si>
+  <si>
+    <t>Install CH3 backlight LED panel</t>
+  </si>
+  <si>
+    <t>(+) J9, (-) J8</t>
+  </si>
+  <si>
+    <t>Bend CH1 and CH2 LEDs, match polarity and height below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Install CH1 LED, set height with cuvette block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">365nm (for DAPI) </t>
+  </si>
+  <si>
+    <t>(+) F1, (-) G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Install CH2 LED, set height with cuvette block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">640nm (for Cy5) </t>
+  </si>
+  <si>
+    <t>(+) F16 (-) G16</t>
+  </si>
+  <si>
+    <t>Install 5V wires</t>
+  </si>
+  <si>
+    <t>B12 - F1 (on leg), E12 - F13, G13 - F16 (on leg), i13 - i10+i9</t>
+  </si>
+  <si>
+    <t>B13 - i7</t>
+  </si>
+  <si>
+    <t>B14 - i1</t>
+  </si>
+  <si>
+    <t>B15- i16</t>
+  </si>
+  <si>
+    <t>B16 - i8</t>
+  </si>
+  <si>
+    <t>pull 6 pins from a spare header</t>
+  </si>
+  <si>
+    <t>use the remaining plastic bar to double the spacer off the A side of the drop board</t>
+  </si>
+  <si>
+    <t>connect the boards at A12 on the cantilever board, A17 on the excitation board</t>
+  </si>
+  <si>
+    <t>STELLA Lab Spec PCR Tube Cantilever Board</t>
+  </si>
+  <si>
+    <t>GH7, …GH12</t>
+  </si>
+  <si>
+    <t>Pull 6 pins from a spare pin header</t>
+  </si>
+  <si>
+    <t>Install the pins, sticking up from the board, into a right angle socket header</t>
+  </si>
+  <si>
+    <t>F7,…F12</t>
+  </si>
+  <si>
     <t>3 pos in three places, 1 pos in six places</t>
   </si>
   <si>
-    <t>1-2ABC, A4, B5, C6, C13, B14, A16, 17ABC</t>
-  </si>
-  <si>
-    <t>Fixture detector board at right angles to cantilever board</t>
-  </si>
-  <si>
-    <t>6 pos right angle pin header</t>
-  </si>
-  <si>
-    <t>G7-12</t>
-  </si>
-  <si>
-    <t>Install socket header for drop board</t>
-  </si>
-  <si>
-    <t>6 pos stacking socket header</t>
-  </si>
-  <si>
-    <t>G1-6</t>
-  </si>
-  <si>
-    <t>Note: for the wiring, install them flat along the F row</t>
-  </si>
-  <si>
-    <t>They can stick up between D, E and F</t>
-  </si>
-  <si>
-    <t>E2-F11</t>
-  </si>
-  <si>
-    <t>E1-F12</t>
-  </si>
-  <si>
-    <t>E15-F10</t>
-  </si>
-  <si>
-    <t>E17-F9</t>
-  </si>
-  <si>
-    <t>E14-F6</t>
-  </si>
-  <si>
-    <t>E13-F5</t>
-  </si>
-  <si>
-    <t>E6-F4</t>
-  </si>
-  <si>
-    <t>E5-F3</t>
-  </si>
-  <si>
-    <t>E4-F2</t>
-  </si>
-  <si>
-    <t>Omit</t>
-  </si>
-  <si>
-    <t>Ground connection</t>
-  </si>
-  <si>
-    <t>at F1</t>
-  </si>
-  <si>
-    <t>STELLA Lab Spec Cuvette Drop Board</t>
-  </si>
-  <si>
-    <t>Proto-Advantage 1.1x1.7”</t>
-  </si>
-  <si>
-    <t>Epoxy color</t>
-  </si>
-  <si>
-    <t>F1-2, F2-3, F3-4, F4-5, F5-6 F6-7</t>
-  </si>
-  <si>
-    <t>install right angle pin headers, long pins towards the edges of the board</t>
-  </si>
-  <si>
-    <t>6 pos, two places</t>
-  </si>
-  <si>
-    <t>B1-6, G1-6</t>
-  </si>
-  <si>
-    <t>Install current limit resistors, short to G pins on header</t>
-  </si>
-  <si>
-    <t>50Ω, three places</t>
-  </si>
-  <si>
-    <t>FG2-C2, FG3-C3, FG4-C4</t>
-  </si>
-  <si>
-    <t>Install channel 0 wires, short to G pin on header</t>
-  </si>
-  <si>
-    <t>FG5-C5</t>
-  </si>
-  <si>
-    <t>Install 5V wire, short to G pin on header</t>
-  </si>
-  <si>
-    <t>FG6-C6</t>
-  </si>
-  <si>
-    <t>STELLA Lab Spec Cuvette Excitation Board</t>
-  </si>
-  <si>
-    <t>F1-G1, F16-G16</t>
-  </si>
-  <si>
-    <t>Install bottom LED, smt</t>
-  </si>
-  <si>
-    <t>488nm</t>
-  </si>
-  <si>
-    <t>(+) FG10, (dot) FG7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trim backlight LED panel (score with knife and snap) </t>
-  </si>
-  <si>
-    <t>Shorten the panel by 15mm</t>
-  </si>
-  <si>
-    <t>Install CH3 backlight LED panel</t>
-  </si>
-  <si>
-    <t>(+) J9, (-) J8</t>
-  </si>
-  <si>
-    <t>Bend CH1 and CH2 LEDs, match polarity and height below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Install CH1 LED, set height with cuvette block </t>
-  </si>
-  <si>
-    <t xml:space="preserve">365nm (for DAPI) </t>
-  </si>
-  <si>
-    <t>(+) F1, (-) G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Install CH2 LED, set height with cuvette block </t>
-  </si>
-  <si>
-    <t xml:space="preserve">640nm (for Cy5) </t>
-  </si>
-  <si>
-    <t>(+) F16 (-) G16</t>
-  </si>
-  <si>
-    <t>Install 5V wires</t>
-  </si>
-  <si>
-    <t>B12 - F1 (on leg), E12 - F13, G13 - F16 (on leg), i13 - i10+i9</t>
-  </si>
-  <si>
-    <t>B13 - i7</t>
-  </si>
-  <si>
-    <t>B14 - i1</t>
-  </si>
-  <si>
-    <t>B15- i16</t>
-  </si>
-  <si>
-    <t>B16 - i8</t>
-  </si>
-  <si>
-    <t>pull 6 pins from a spare header</t>
-  </si>
-  <si>
-    <t>use the remaining plastic bar to double the spacer off the A side of the drop board</t>
-  </si>
-  <si>
-    <t>connect the boards at A12 on the cantilever board, A17 on the excitation board</t>
-  </si>
-  <si>
-    <t>STELLA Lab Spec PCR Tube Cantilever Board</t>
-  </si>
-  <si>
-    <t>GH7, …GH12</t>
-  </si>
-  <si>
-    <t>Pull 6 pins from a spare pin header</t>
-  </si>
-  <si>
-    <t>Install the pins, sticking up from the board, into a right angle socket header</t>
-  </si>
-  <si>
-    <t>F7,…F12</t>
-  </si>
-  <si>
     <t>1ABC, A4, B5, C6, C13, B14, A16, 17ABC</t>
   </si>
   <si>
@@ -990,6 +1108,285 @@
   </si>
   <si>
     <t>REAR: G4 - G1</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>units</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>hfe ~ gain PN2222</t>
+  </si>
+  <si>
+    <t>max current</t>
+  </si>
+  <si>
+    <t>mA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base current </t>
+  </si>
+  <si>
+    <t>base resistor</t>
+  </si>
+  <si>
+    <t>Ω</t>
+  </si>
+  <si>
+    <t>BE voltage</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>DAC max</t>
+  </si>
+  <si>
+    <t>Supply</t>
+  </si>
+  <si>
+    <t>DAC max / Supply</t>
+  </si>
+  <si>
+    <t>DAC set max</t>
+  </si>
+  <si>
+    <t>DAC use max</t>
+  </si>
+  <si>
+    <t>DAC nominal max</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>program action</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERFACE TESTS: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">date correct </t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>time correct and live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selection change on rotary </t>
+  </si>
+  <si>
+    <t>correct selection order</t>
+  </si>
+  <si>
+    <t>push when main selected</t>
+  </si>
+  <si>
+    <t>go to main page</t>
+  </si>
+  <si>
+    <t>push when B+ selected</t>
+  </si>
+  <si>
+    <t>increment batch number</t>
+  </si>
+  <si>
+    <t>batch number correct</t>
+  </si>
+  <si>
+    <t>battery % correct</t>
+  </si>
+  <si>
+    <t>status correct</t>
+  </si>
+  <si>
+    <t>status highlight color correct</t>
+  </si>
+  <si>
+    <t>measure button color correct</t>
+  </si>
+  <si>
+    <t>push when measure selected</t>
+  </si>
+  <si>
+    <t>run measurement sequence</t>
+  </si>
+  <si>
+    <t>push when excitation selected</t>
+  </si>
+  <si>
+    <t>selectable, green</t>
+  </si>
+  <si>
+    <t>second push when excitation selected</t>
+  </si>
+  <si>
+    <t>not selectable, white</t>
+  </si>
+  <si>
+    <t>rotate when excitation selectable</t>
+  </si>
+  <si>
+    <t>cycle lamp choice</t>
+  </si>
+  <si>
+    <t>make this list wrap around</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>excitation lamp ID correct</t>
+  </si>
+  <si>
+    <t>push when current selected</t>
+  </si>
+  <si>
+    <t>selectable, green, show REQ</t>
+  </si>
+  <si>
+    <t>second push when current selected</t>
+  </si>
+  <si>
+    <t>not selectable, white, show last</t>
+  </si>
+  <si>
+    <t>rotate when current selectable</t>
+  </si>
+  <si>
+    <t>change REQ %</t>
+  </si>
+  <si>
+    <t>current percentage or last correct</t>
+  </si>
+  <si>
+    <t>push when gain selected</t>
+  </si>
+  <si>
+    <t>second push when gain selected</t>
+  </si>
+  <si>
+    <t>rotate when gain selectable</t>
+  </si>
+  <si>
+    <t>change gain</t>
+  </si>
+  <si>
+    <t>gain correct</t>
+  </si>
+  <si>
+    <t>push when integration selected</t>
+  </si>
+  <si>
+    <t>second push when integration selected</t>
+  </si>
+  <si>
+    <t>rotate when integration selectable</t>
+  </si>
+  <si>
+    <t>change integration</t>
+  </si>
+  <si>
+    <t>integration correct</t>
+  </si>
+  <si>
+    <t>push when view A selected</t>
+  </si>
+  <si>
+    <t>second push when view A selected</t>
+  </si>
+  <si>
+    <t>rotate when view A selectable</t>
+  </si>
+  <si>
+    <t>change view A channel</t>
+  </si>
+  <si>
+    <t>view A correct</t>
+  </si>
+  <si>
+    <t>push when view B selected</t>
+  </si>
+  <si>
+    <t>second push when view B selected</t>
+  </si>
+  <si>
+    <t>rotate when view B selectable</t>
+  </si>
+  <si>
+    <t>change view B channel</t>
+  </si>
+  <si>
+    <t>view B correct</t>
+  </si>
+  <si>
+    <t>show A B choice collision warning colors</t>
+  </si>
+  <si>
+    <t>instruction line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD </t>
+  </si>
+  <si>
+    <t>not implemented yet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">back arrow </t>
+  </si>
+  <si>
+    <t>DO</t>
+  </si>
+  <si>
+    <t>next arrow</t>
+  </si>
+  <si>
+    <t>M number correct</t>
+  </si>
+  <si>
+    <t>A value correct</t>
+  </si>
+  <si>
+    <t>B value correct</t>
+  </si>
+  <si>
+    <t>Ratio correct</t>
+  </si>
+  <si>
+    <t>%DR correct</t>
+  </si>
+  <si>
+    <t>make mmt display values change with A B choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNCTIONAL TESTS: </t>
+  </si>
+  <si>
+    <t>read current on lamp choice ADC channel</t>
+  </si>
+  <si>
+    <t>assign correct part numbers to each lamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADD FUNCTIONALITY: </t>
+  </si>
+  <si>
+    <t>work with as7343 sensor</t>
+  </si>
+  <si>
+    <t>accept configuration file to describe lamps</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1396,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -1025,6 +1422,12 @@
     <font>
       <sz val="10"/>
       <color indexed="13"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
@@ -1096,7 +1499,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1451,6 +1854,51 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="14"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="17"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="10"/>
       </left>
       <right style="thin">
@@ -1485,7 +1933,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1543,6 +1991,9 @@
     <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1575,6 +2026,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1645,22 +2105,31 @@
     <xf numFmtId="49" fontId="0" fillId="11" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -1685,6 +2154,27 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2757,10 +3247,11 @@
     <col min="3" max="3" width="33.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="4.17188" style="1" customWidth="1"/>
     <col min="5" max="7" width="16.3516" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.1719" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.8516" style="1" customWidth="1"/>
     <col min="9" max="9" width="4.85156" style="1" customWidth="1"/>
     <col min="10" max="13" width="5.67188" style="1" customWidth="1"/>
-    <col min="14" max="15" width="70.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="92.8516" style="1" customWidth="1"/>
+    <col min="15" max="15" width="70.5" style="1" customWidth="1"/>
     <col min="16" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2830,7 +3321,7 @@
     </row>
     <row r="3" ht="20.25" customHeight="1">
       <c r="A3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s" s="6">
         <v>15</v>
@@ -2851,18 +3342,18 @@
         <v>19</v>
       </c>
       <c r="H3" s="8">
-        <v>1083</v>
+        <v>1609</v>
       </c>
       <c r="I3" s="8">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="J3" s="8" cm="1">
         <f t="array" ref="J3">I3*D3</f>
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="K3" s="8" cm="1">
         <f t="array" ref="K3">SUMIF(B3,"LS",J3)</f>
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="L3" s="8" cm="1">
         <f t="array" ref="L3">SUMIF(B3,"C2",J3)</f>
@@ -2877,10 +3368,10 @@
     </row>
     <row r="4" ht="20.05" customHeight="1">
       <c r="A4" s="10">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s" s="12">
         <v>20</v>
@@ -2889,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="s" s="12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s" s="12">
         <v>18</v>
@@ -2898,22 +3389,22 @@
         <v>19</v>
       </c>
       <c r="H4" s="13">
-        <v>4698</v>
+        <v>5358</v>
       </c>
       <c r="I4" s="13">
-        <v>19</v>
+        <v>6.5</v>
       </c>
       <c r="J4" s="13" cm="1">
         <f t="array" ref="J4">I4*D4</f>
-        <v>19</v>
+        <v>6.5</v>
       </c>
       <c r="K4" s="13" cm="1">
         <f t="array" ref="K4">SUMIF(B4,"LS",J4)</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L4" s="13" cm="1">
         <f t="array" ref="L4">SUMIF(B4,"C2",J4)</f>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M4" s="13" cm="1">
         <f t="array" ref="M4">SUMIF(B4,"P2",J4)</f>
@@ -2924,19 +3415,19 @@
     </row>
     <row r="5" ht="20.05" customHeight="1">
       <c r="A5" s="10">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s" s="12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="13">
         <v>1</v>
       </c>
       <c r="E5" t="s" s="12">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s" s="12">
         <v>18</v>
@@ -2945,18 +3436,18 @@
         <v>19</v>
       </c>
       <c r="H5" s="13">
-        <v>4698</v>
+        <v>5360</v>
       </c>
       <c r="I5" s="13">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J5" s="13" cm="1">
         <f t="array" ref="J5">I5*D5</f>
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K5" s="13" cm="1">
         <f t="array" ref="K5">SUMIF(B5,"LS",J5)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L5" s="13" cm="1">
         <f t="array" ref="L5">SUMIF(B5,"C2",J5)</f>
@@ -2964,20 +3455,20 @@
       </c>
       <c r="M5" s="13" cm="1">
         <f t="array" ref="M5">SUMIF(B5,"P2",J5)</f>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
     <row r="6" ht="20.05" customHeight="1">
       <c r="A6" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s" s="11">
         <v>15</v>
       </c>
       <c r="C6" t="s" s="12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="13">
         <v>1</v>
@@ -2992,18 +3483,18 @@
         <v>19</v>
       </c>
       <c r="H6" s="13">
-        <v>1609</v>
+        <v>1083</v>
       </c>
       <c r="I6" s="13">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="J6" s="13" cm="1">
         <f t="array" ref="J6">I6*D6</f>
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="K6" s="13" cm="1">
         <f t="array" ref="K6">SUMIF(B6,"LS",J6)</f>
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="L6" s="13" cm="1">
         <f t="array" ref="L6">SUMIF(B6,"C2",J6)</f>
@@ -3024,7 +3515,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s" s="12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="13">
         <v>1</v>
@@ -3065,16 +3556,16 @@
     </row>
     <row r="8" ht="20.05" customHeight="1">
       <c r="A8" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s" s="11">
         <v>15</v>
       </c>
       <c r="C8" t="s" s="12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" t="s" s="12">
         <v>17</v>
@@ -3083,21 +3574,21 @@
         <v>18</v>
       </c>
       <c r="G8" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H8" s="13">
-        <v>5360</v>
+        <v>25</v>
+      </c>
+      <c r="H8" t="s" s="12">
+        <v>26</v>
       </c>
       <c r="I8" s="13">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J8" s="13" cm="1">
         <f t="array" ref="J8">I8*D8</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K8" s="13" cm="1">
         <f t="array" ref="K8">SUMIF(B8,"LS",J8)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L8" s="13" cm="1">
         <f t="array" ref="L8">SUMIF(B8,"C2",J8)</f>
@@ -3112,16 +3603,16 @@
     </row>
     <row r="9" ht="20.05" customHeight="1">
       <c r="A9" s="10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s" s="11">
         <v>15</v>
       </c>
       <c r="C9" t="s" s="12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="s" s="12">
         <v>17</v>
@@ -3130,21 +3621,21 @@
         <v>18</v>
       </c>
       <c r="G9" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H9" s="13">
-        <v>5358</v>
+        <v>25</v>
+      </c>
+      <c r="H9" t="s" s="12">
+        <v>28</v>
       </c>
       <c r="I9" s="13">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="J9" s="13" cm="1">
         <f t="array" ref="J9">I9*D9</f>
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="K9" s="13" cm="1">
         <f t="array" ref="K9">SUMIF(B9,"LS",J9)</f>
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="L9" s="13" cm="1">
         <f t="array" ref="L9">SUMIF(B9,"C2",J9)</f>
@@ -3159,43 +3650,43 @@
     </row>
     <row r="10" ht="20.05" customHeight="1">
       <c r="A10" s="10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s" s="11">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s" s="12">
         <v>29</v>
       </c>
-      <c r="B10" t="s" s="11">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s" s="12">
-        <v>27</v>
-      </c>
       <c r="D10" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10" t="s" s="12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G10" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H10" s="13">
-        <v>1626</v>
+        <v>25</v>
+      </c>
+      <c r="H10" t="s" s="12">
+        <v>30</v>
       </c>
       <c r="I10" s="13">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J10" s="13" cm="1">
         <f t="array" ref="J10">I10*D10</f>
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="K10" s="13" cm="1">
         <f t="array" ref="K10">SUMIF(B10,"LS",J10)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L10" s="13" cm="1">
         <f t="array" ref="L10">SUMIF(B10,"C2",J10)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="13" cm="1">
         <f t="array" ref="M10">SUMIF(B10,"P2",J10)</f>
@@ -3206,88 +3697,86 @@
     </row>
     <row r="11" ht="20.05" customHeight="1">
       <c r="A11" s="10">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s" s="12">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D11" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="s" s="12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G11" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H11" s="13">
-        <v>392</v>
+        <v>25</v>
+      </c>
+      <c r="H11" t="s" s="12">
+        <v>32</v>
       </c>
       <c r="I11" s="13">
         <v>0.1</v>
       </c>
       <c r="J11" s="13" cm="1">
         <f t="array" ref="J11">I11*D11</f>
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="K11" s="13" cm="1">
         <f t="array" ref="K11">SUMIF(B11,"LS",J11)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L11" s="13" cm="1">
         <f t="array" ref="L11">SUMIF(B11,"C2",J11)</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="13" cm="1">
         <f t="array" ref="M11">SUMIF(B11,"P2",J11)</f>
         <v>0</v>
       </c>
-      <c r="N11" t="s" s="12">
-        <v>29</v>
-      </c>
+      <c r="N11" s="14"/>
       <c r="O11" s="14"/>
     </row>
     <row r="12" ht="20.05" customHeight="1">
       <c r="A12" s="10">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s" s="12">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D12" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s" s="12">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G12" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H12" s="13">
-        <v>392</v>
+        <v>25</v>
+      </c>
+      <c r="H12" t="s" s="12">
+        <v>34</v>
       </c>
       <c r="I12" s="13">
         <v>0.1</v>
       </c>
       <c r="J12" s="13" cm="1">
         <f t="array" ref="J12">I12*D12</f>
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="K12" s="13" cm="1">
         <f t="array" ref="K12">SUMIF(B12,"LS",J12)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L12" s="13" cm="1">
         <f t="array" ref="L12">SUMIF(B12,"C2",J12)</f>
@@ -3295,48 +3784,46 @@
       </c>
       <c r="M12" s="13" cm="1">
         <f t="array" ref="M12">SUMIF(B12,"P2",J12)</f>
-        <v>0.1</v>
-      </c>
-      <c r="N12" t="s" s="12">
-        <v>29</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N12" s="14"/>
       <c r="O12" s="14"/>
     </row>
     <row r="13" ht="20.05" customHeight="1">
       <c r="A13" s="10">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s" s="12">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D13" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="s" s="12">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G13" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H13" s="13">
-        <v>392</v>
+        <v>25</v>
+      </c>
+      <c r="H13" t="s" s="12">
+        <v>36</v>
       </c>
       <c r="I13" s="13">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="J13" s="13" cm="1">
         <f t="array" ref="J13">I13*D13</f>
-        <v>0.1</v>
+        <v>5.2</v>
       </c>
       <c r="K13" s="13" cm="1">
         <f t="array" ref="K13">SUMIF(B13,"LS",J13)</f>
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L13" s="13" cm="1">
         <f t="array" ref="L13">SUMIF(B13,"C2",J13)</f>
@@ -3344,142 +3831,136 @@
       </c>
       <c r="M13" s="13" cm="1">
         <f t="array" ref="M13">SUMIF(B13,"P2",J13)</f>
-        <v>0.1</v>
-      </c>
-      <c r="N13" t="s" s="12">
-        <v>29</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N13" s="14"/>
       <c r="O13" s="14"/>
     </row>
     <row r="14" ht="20.05" customHeight="1">
       <c r="A14" s="10">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s" s="12">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D14" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s" s="12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G14" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H14" s="13">
-        <v>1540</v>
+        <v>25</v>
+      </c>
+      <c r="H14" t="s" s="12">
+        <v>38</v>
       </c>
       <c r="I14" s="13">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="13" cm="1">
         <f t="array" ref="J14">I14*D14</f>
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K14" s="13" cm="1">
         <f t="array" ref="K14">SUMIF(B14,"LS",J14)</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L14" s="13" cm="1">
         <f t="array" ref="L14">SUMIF(B14,"C2",J14)</f>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="13" cm="1">
         <f t="array" ref="M14">SUMIF(B14,"P2",J14)</f>
         <v>0</v>
       </c>
-      <c r="N14" t="s" s="12">
-        <v>32</v>
-      </c>
+      <c r="N14" s="14"/>
       <c r="O14" s="14"/>
     </row>
     <row r="15" ht="20.05" customHeight="1">
       <c r="A15" s="10">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s" s="12">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D15" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E15" t="s" s="12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G15" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H15" s="13">
-        <v>392</v>
+        <v>25</v>
+      </c>
+      <c r="H15" t="s" s="12">
+        <v>40</v>
       </c>
       <c r="I15" s="13">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J15" s="13" cm="1">
         <f t="array" ref="J15">I15*D15</f>
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K15" s="13" cm="1">
         <f t="array" ref="K15">SUMIF(B15,"LS",J15)</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L15" s="13" cm="1">
         <f t="array" ref="L15">SUMIF(B15,"C2",J15)</f>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M15" s="13" cm="1">
         <f t="array" ref="M15">SUMIF(B15,"P2",J15)</f>
         <v>0</v>
       </c>
-      <c r="N15" t="s" s="12">
-        <v>29</v>
-      </c>
+      <c r="N15" s="14"/>
       <c r="O15" s="14"/>
     </row>
     <row r="16" ht="20.05" customHeight="1">
       <c r="A16" s="10">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="11">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s" s="12">
+        <v>41</v>
+      </c>
+      <c r="D16" s="13">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s" s="12">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s" s="12">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s" s="12">
+        <v>43</v>
+      </c>
+      <c r="H16" t="s" s="12">
         <v>44</v>
       </c>
-      <c r="B16" t="s" s="11">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s" s="12">
-        <v>33</v>
-      </c>
-      <c r="D16" s="13">
-        <v>12</v>
-      </c>
-      <c r="E16" t="s" s="12">
-        <v>22</v>
-      </c>
-      <c r="F16" t="s" s="12">
-        <v>18</v>
-      </c>
-      <c r="G16" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H16" s="13">
-        <v>392</v>
-      </c>
       <c r="I16" s="13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="13" cm="1">
         <f t="array" ref="J16">I16*D16</f>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="13" cm="1">
         <f t="array" ref="K16">SUMIF(B16,"LS",J16)</f>
@@ -3491,99 +3972,104 @@
       </c>
       <c r="M16" s="13" cm="1">
         <f t="array" ref="M16">SUMIF(B16,"P2",J16)</f>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="s" s="12">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="O16" s="14"/>
     </row>
     <row r="17" ht="20.05" customHeight="1">
       <c r="A17" s="10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s" s="12">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D17" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s" s="12">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s" s="12">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G17" t="s" s="12">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="H17" t="s" s="12">
-        <v>36</v>
-      </c>
-      <c r="I17" s="13">
-        <v>0.1</v>
+        <v>50</v>
+      </c>
+      <c r="I17" s="13" cm="1">
+        <f t="array" ref="I17">30/100</f>
+        <v>0.3</v>
       </c>
       <c r="J17" s="13" cm="1">
         <f t="array" ref="J17">I17*D17</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K17" s="13" cm="1">
         <f t="array" ref="K17">SUMIF(B17,"LS",J17)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L17" s="13" cm="1">
         <f t="array" ref="L17">SUMIF(B17,"C2",J17)</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M17" s="13" cm="1">
         <f t="array" ref="M17">SUMIF(B17,"P2",J17)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
+      <c r="N17" t="s" s="12">
+        <v>51</v>
+      </c>
+      <c r="O17" t="s" s="12">
+        <v>52</v>
+      </c>
     </row>
     <row r="18" ht="20.05" customHeight="1">
       <c r="A18" s="10">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s" s="12">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D18" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" t="s" s="12">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G18" t="s" s="12">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s" s="12">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I18" s="13">
-        <v>0.1</v>
+        <v>4.3</v>
       </c>
       <c r="J18" s="13" cm="1">
         <f t="array" ref="J18">I18*D18</f>
-        <v>0.4</v>
+        <v>8.6</v>
       </c>
       <c r="K18" s="13" cm="1">
         <f t="array" ref="K18">SUMIF(B18,"LS",J18)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L18" s="13" cm="1">
         <f t="array" ref="L18">SUMIF(B18,"C2",J18)</f>
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="M18" s="13" cm="1">
         <f t="array" ref="M18">SUMIF(B18,"P2",J18)</f>
@@ -3594,35 +4080,35 @@
     </row>
     <row r="19" ht="20.05" customHeight="1">
       <c r="A19" s="10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s" s="11">
         <v>12</v>
       </c>
       <c r="C19" t="s" s="12">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D19" s="13">
         <v>1</v>
       </c>
       <c r="E19" t="s" s="12">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G19" t="s" s="12">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="H19" t="s" s="12">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="I19" s="13">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J19" s="13" cm="1">
         <f t="array" ref="J19">I19*D19</f>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K19" s="13" cm="1">
         <f t="array" ref="K19">SUMIF(B19,"LS",J19)</f>
@@ -3630,46 +4116,48 @@
       </c>
       <c r="L19" s="13" cm="1">
         <f t="array" ref="L19">SUMIF(B19,"C2",J19)</f>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M19" s="13" cm="1">
         <f t="array" ref="M19">SUMIF(B19,"P2",J19)</f>
         <v>0</v>
       </c>
-      <c r="N19" s="14"/>
+      <c r="N19" t="s" s="12">
+        <v>58</v>
+      </c>
       <c r="O19" s="14"/>
     </row>
     <row r="20" ht="20.05" customHeight="1">
       <c r="A20" s="10">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s" s="12">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D20" s="13">
         <v>1</v>
       </c>
       <c r="E20" t="s" s="12">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G20" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="H20" t="s" s="12">
-        <v>40</v>
+        <v>19</v>
+      </c>
+      <c r="H20" s="13">
+        <v>4698</v>
       </c>
       <c r="I20" s="13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="13" cm="1">
         <f t="array" ref="J20">I20*D20</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="13" cm="1">
         <f t="array" ref="K20">SUMIF(B20,"LS",J20)</f>
@@ -3677,93 +4165,95 @@
       </c>
       <c r="L20" s="13" cm="1">
         <f t="array" ref="L20">SUMIF(B20,"C2",J20)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M20" s="13" cm="1">
         <f t="array" ref="M20">SUMIF(B20,"P2",J20)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14"/>
       <c r="O20" s="14"/>
     </row>
     <row r="21" ht="20.05" customHeight="1">
       <c r="A21" s="10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s" s="12">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D21" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s" s="12">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G21" t="s" s="12">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="H21" t="s" s="12">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="I21" s="13">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J21" s="13" cm="1">
         <f t="array" ref="J21">I21*D21</f>
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="K21" s="13" cm="1">
         <f t="array" ref="K21">SUMIF(B21,"LS",J21)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L21" s="13" cm="1">
         <f t="array" ref="L21">SUMIF(B21,"C2",J21)</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M21" s="13" cm="1">
         <f t="array" ref="M21">SUMIF(B21,"P2",J21)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="14"/>
+      <c r="N21" t="s" s="12">
+        <v>62</v>
+      </c>
       <c r="O21" s="14"/>
     </row>
     <row r="22" ht="20.05" customHeight="1">
       <c r="A22" s="10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s" s="11">
         <v>12</v>
       </c>
       <c r="C22" t="s" s="12">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D22" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s" s="12">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G22" t="s" s="12">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H22" t="s" s="12">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="I22" s="13">
-        <v>0.1</v>
+        <v>18</v>
       </c>
       <c r="J22" s="13" cm="1">
         <f t="array" ref="J22">I22*D22</f>
-        <v>0.2</v>
+        <v>18</v>
       </c>
       <c r="K22" s="13" cm="1">
         <f t="array" ref="K22">SUMIF(B22,"LS",J22)</f>
@@ -3771,7 +4261,7 @@
       </c>
       <c r="L22" s="13" cm="1">
         <f t="array" ref="L22">SUMIF(B22,"C2",J22)</f>
-        <v>0.2</v>
+        <v>18</v>
       </c>
       <c r="M22" s="13" cm="1">
         <f t="array" ref="M22">SUMIF(B22,"P2",J22)</f>
@@ -3782,35 +4272,35 @@
     </row>
     <row r="23" ht="20.05" customHeight="1">
       <c r="A23" s="10">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s" s="12">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D23" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="s" s="12">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G23" t="s" s="12">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H23" t="s" s="12">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="I23" s="13">
-        <v>0.1</v>
+        <v>2.75</v>
       </c>
       <c r="J23" s="13" cm="1">
         <f t="array" ref="J23">I23*D23</f>
-        <v>0.2</v>
+        <v>2.75</v>
       </c>
       <c r="K23" s="13" cm="1">
         <f t="array" ref="K23">SUMIF(B23,"LS",J23)</f>
@@ -3818,46 +4308,46 @@
       </c>
       <c r="L23" s="13" cm="1">
         <f t="array" ref="L23">SUMIF(B23,"C2",J23)</f>
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M23" s="13" cm="1">
         <f t="array" ref="M23">SUMIF(B23,"P2",J23)</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
     </row>
     <row r="24" ht="20.05" customHeight="1">
       <c r="A24" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s" s="11">
         <v>12</v>
       </c>
       <c r="C24" t="s" s="12">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D24" s="13">
         <v>1</v>
       </c>
       <c r="E24" t="s" s="12">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G24" t="s" s="12">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="H24" t="s" s="12">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="I24" s="13">
-        <v>2.75</v>
+        <v>1</v>
       </c>
       <c r="J24" s="13" cm="1">
         <f t="array" ref="J24">I24*D24</f>
-        <v>2.75</v>
+        <v>1</v>
       </c>
       <c r="K24" s="13" cm="1">
         <f t="array" ref="K24">SUMIF(B24,"LS",J24)</f>
@@ -3865,46 +4355,48 @@
       </c>
       <c r="L24" s="13" cm="1">
         <f t="array" ref="L24">SUMIF(B24,"C2",J24)</f>
-        <v>2.75</v>
+        <v>1</v>
       </c>
       <c r="M24" s="13" cm="1">
         <f t="array" ref="M24">SUMIF(B24,"P2",J24)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="14"/>
+      <c r="N24" t="s" s="12">
+        <v>70</v>
+      </c>
       <c r="O24" s="14"/>
     </row>
     <row r="25" ht="20.05" customHeight="1">
       <c r="A25" s="10">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s" s="12">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D25" s="13">
         <v>1</v>
       </c>
       <c r="E25" t="s" s="12">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F25" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G25" t="s" s="12">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H25" t="s" s="12">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="I25" s="13">
-        <v>2.75</v>
+        <v>0.53</v>
       </c>
       <c r="J25" s="13" cm="1">
         <f t="array" ref="J25">I25*D25</f>
-        <v>2.75</v>
+        <v>0.53</v>
       </c>
       <c r="K25" s="13" cm="1">
         <f t="array" ref="K25">SUMIF(B25,"LS",J25)</f>
@@ -3912,148 +4404,152 @@
       </c>
       <c r="L25" s="13" cm="1">
         <f t="array" ref="L25">SUMIF(B25,"C2",J25)</f>
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M25" s="13" cm="1">
         <f t="array" ref="M25">SUMIF(B25,"P2",J25)</f>
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N25" s="14"/>
       <c r="O25" s="14"/>
     </row>
     <row r="26" ht="20.05" customHeight="1">
       <c r="A26" s="10">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s" s="12">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D26" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s" s="12">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G26" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="H26" t="s" s="12">
-        <v>46</v>
+        <v>19</v>
+      </c>
+      <c r="H26" s="13">
+        <v>392</v>
       </c>
       <c r="I26" s="13">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J26" s="13" cm="1">
         <f t="array" ref="J26">I26*D26</f>
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="K26" s="13" cm="1">
         <f t="array" ref="K26">SUMIF(B26,"LS",J26)</f>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="13" cm="1">
         <f t="array" ref="L26">SUMIF(B26,"C2",J26)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M26" s="13" cm="1">
         <f t="array" ref="M26">SUMIF(B26,"P2",J26)</f>
         <v>0</v>
       </c>
-      <c r="N26" s="14"/>
+      <c r="N26" t="s" s="12">
+        <v>74</v>
+      </c>
       <c r="O26" s="14"/>
     </row>
     <row r="27" ht="20.05" customHeight="1">
       <c r="A27" s="10">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s" s="12">
+        <v>75</v>
+      </c>
+      <c r="D27" s="13">
+        <v>6</v>
+      </c>
+      <c r="E27" t="s" s="12">
         <v>47</v>
-      </c>
-      <c r="D27" s="13">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s" s="12">
-        <v>17</v>
       </c>
       <c r="F27" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G27" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="H27" t="s" s="12">
-        <v>48</v>
+        <v>19</v>
+      </c>
+      <c r="H27" s="13">
+        <v>392</v>
       </c>
       <c r="I27" s="13">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J27" s="13" cm="1">
         <f t="array" ref="J27">I27*D27</f>
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" s="13" cm="1">
         <f t="array" ref="K27">SUMIF(B27,"LS",J27)</f>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L27" s="13" cm="1">
         <f t="array" ref="L27">SUMIF(B27,"C2",J27)</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M27" s="13" cm="1">
         <f t="array" ref="M27">SUMIF(B27,"P2",J27)</f>
         <v>0</v>
       </c>
-      <c r="N27" s="14"/>
+      <c r="N27" t="s" s="12">
+        <v>74</v>
+      </c>
       <c r="O27" s="14"/>
     </row>
     <row r="28" ht="20.05" customHeight="1">
       <c r="A28" s="10">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s" s="11">
         <v>12</v>
       </c>
-      <c r="B28" t="s" s="11">
-        <v>15</v>
-      </c>
       <c r="C28" t="s" s="12">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D28" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="s" s="12">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G28" t="s" s="12">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H28" t="s" s="12">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I28" s="13">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J28" s="13" cm="1">
         <f t="array" ref="J28">I28*D28</f>
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="K28" s="13" cm="1">
         <f t="array" ref="K28">SUMIF(B28,"LS",J28)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="13" cm="1">
         <f t="array" ref="L28">SUMIF(B28,"C2",J28)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M28" s="13" cm="1">
         <f t="array" ref="M28">SUMIF(B28,"P2",J28)</f>
@@ -4064,43 +4560,43 @@
     </row>
     <row r="29" ht="20.05" customHeight="1">
       <c r="A29" s="10">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s" s="12">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D29" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s" s="12">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G29" t="s" s="12">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H29" t="s" s="12">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I29" s="13">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="13" cm="1">
         <f t="array" ref="J29">I29*D29</f>
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="K29" s="13" cm="1">
         <f t="array" ref="K29">SUMIF(B29,"LS",J29)</f>
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="13" cm="1">
         <f t="array" ref="L29">SUMIF(B29,"C2",J29)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M29" s="13" cm="1">
         <f t="array" ref="M29">SUMIF(B29,"P2",J29)</f>
@@ -4111,35 +4607,35 @@
     </row>
     <row r="30" ht="20.05" customHeight="1">
       <c r="A30" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s" s="11">
         <v>12</v>
       </c>
       <c r="C30" t="s" s="12">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="D30" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="s" s="12">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G30" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="H30" t="s" s="12">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="H30" s="13">
+        <v>1540</v>
       </c>
       <c r="I30" s="13">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J30" s="13" cm="1">
         <f t="array" ref="J30">I30*D30</f>
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="K30" s="13" cm="1">
         <f t="array" ref="K30">SUMIF(B30,"LS",J30)</f>
@@ -4147,46 +4643,48 @@
       </c>
       <c r="L30" s="13" cm="1">
         <f t="array" ref="L30">SUMIF(B30,"C2",J30)</f>
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="M30" s="13" cm="1">
         <f t="array" ref="M30">SUMIF(B30,"P2",J30)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="14"/>
+      <c r="N30" t="s" s="12">
+        <v>78</v>
+      </c>
       <c r="O30" s="14"/>
     </row>
     <row r="31" ht="20.05" customHeight="1">
       <c r="A31" s="10">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s" s="12">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="D31" s="13">
         <v>1</v>
       </c>
       <c r="E31" t="s" s="12">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G31" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="H31" t="s" s="12">
-        <v>56</v>
+        <v>19</v>
+      </c>
+      <c r="H31" s="13">
+        <v>1626</v>
       </c>
       <c r="I31" s="13">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" cm="1">
         <f t="array" ref="J31">I31*D31</f>
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="K31" s="13" cm="1">
         <f t="array" ref="K31">SUMIF(B31,"LS",J31)</f>
@@ -4194,50 +4692,50 @@
       </c>
       <c r="L31" s="13" cm="1">
         <f t="array" ref="L31">SUMIF(B31,"C2",J31)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" s="13" cm="1">
         <f t="array" ref="M31">SUMIF(B31,"P2",J31)</f>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
     </row>
     <row r="32" ht="20.05" customHeight="1">
       <c r="A32" s="10">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s" s="12">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="D32" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32" t="s" s="12">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s" s="12">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s" s="12">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H32" t="s" s="12">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="I32" s="13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J32" s="13" cm="1">
         <f t="array" ref="J32">I32*D32</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" s="13" cm="1">
         <f t="array" ref="K32">SUMIF(B32,"LS",J32)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="13" cm="1">
         <f t="array" ref="L32">SUMIF(B32,"C2",J32)</f>
@@ -4247,40 +4745,42 @@
         <f t="array" ref="M32">SUMIF(B32,"P2",J32)</f>
         <v>0</v>
       </c>
-      <c r="N32" s="14"/>
+      <c r="N32" t="s" s="12">
+        <v>45</v>
+      </c>
       <c r="O32" s="14"/>
     </row>
     <row r="33" ht="20.05" customHeight="1">
       <c r="A33" s="10">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s" s="11">
         <v>12</v>
       </c>
       <c r="C33" t="s" s="12">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D33" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="s" s="12">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s" s="12">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G33" t="s" s="12">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H33" t="s" s="12">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="I33" s="13">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="13" cm="1">
         <f t="array" ref="J33">I33*D33</f>
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="K33" s="13" cm="1">
         <f t="array" ref="K33">SUMIF(B33,"LS",J33)</f>
@@ -4288,46 +4788,48 @@
       </c>
       <c r="L33" s="13" cm="1">
         <f t="array" ref="L33">SUMIF(B33,"C2",J33)</f>
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" cm="1">
         <f t="array" ref="M33">SUMIF(B33,"P2",J33)</f>
         <v>0</v>
       </c>
-      <c r="N33" s="14"/>
+      <c r="N33" t="s" s="12">
+        <v>82</v>
+      </c>
       <c r="O33" s="14"/>
     </row>
     <row r="34" ht="20.05" customHeight="1">
       <c r="A34" s="10">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s" s="12">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="D34" s="13">
         <v>1</v>
       </c>
       <c r="E34" t="s" s="12">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F34" t="s" s="12">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G34" t="s" s="12">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H34" t="s" s="12">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="I34" s="13">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J34" s="13" cm="1">
         <f t="array" ref="J34">I34*D34</f>
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="K34" s="13" cm="1">
         <f t="array" ref="K34">SUMIF(B34,"LS",J34)</f>
@@ -4339,42 +4841,44 @@
       </c>
       <c r="M34" s="13" cm="1">
         <f t="array" ref="M34">SUMIF(B34,"P2",J34)</f>
-        <v>4.3</v>
-      </c>
-      <c r="N34" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="N34" t="s" s="12">
+        <v>82</v>
+      </c>
       <c r="O34" s="14"/>
     </row>
     <row r="35" ht="20.05" customHeight="1">
       <c r="A35" s="10">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s" s="11">
         <v>12</v>
       </c>
       <c r="C35" t="s" s="12">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D35" s="13">
         <v>1</v>
       </c>
       <c r="E35" t="s" s="12">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F35" t="s" s="12">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G35" t="s" s="12">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H35" t="s" s="12">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="I35" s="13">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="J35" s="13" cm="1">
         <f t="array" ref="J35">I35*D35</f>
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="K35" s="13" cm="1">
         <f t="array" ref="K35">SUMIF(B35,"LS",J35)</f>
@@ -4382,46 +4886,48 @@
       </c>
       <c r="L35" s="13" cm="1">
         <f t="array" ref="L35">SUMIF(B35,"C2",J35)</f>
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M35" s="13" cm="1">
         <f t="array" ref="M35">SUMIF(B35,"P2",J35)</f>
         <v>0</v>
       </c>
-      <c r="N35" s="14"/>
+      <c r="N35" t="s" s="12">
+        <v>82</v>
+      </c>
       <c r="O35" s="14"/>
     </row>
     <row r="36" ht="20.05" customHeight="1">
       <c r="A36" s="10">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s" s="11">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s" s="12">
+        <v>85</v>
+      </c>
+      <c r="D36" s="13">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s" s="12">
+        <v>47</v>
+      </c>
+      <c r="F36" t="s" s="12">
         <v>42</v>
       </c>
-      <c r="B36" t="s" s="11">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s" s="12">
-        <v>60</v>
-      </c>
-      <c r="D36" s="13">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s" s="12">
-        <v>22</v>
-      </c>
-      <c r="F36" t="s" s="12">
-        <v>18</v>
-      </c>
       <c r="G36" t="s" s="12">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H36" t="s" s="12">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="I36" s="13">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="J36" s="13" cm="1">
         <f t="array" ref="J36">I36*D36</f>
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="K36" s="13" cm="1">
         <f t="array" ref="K36">SUMIF(B36,"LS",J36)</f>
@@ -4433,42 +4939,44 @@
       </c>
       <c r="M36" s="13" cm="1">
         <f t="array" ref="M36">SUMIF(B36,"P2",J36)</f>
-        <v>0.53</v>
-      </c>
-      <c r="N36" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="N36" t="s" s="12">
+        <v>82</v>
+      </c>
       <c r="O36" s="14"/>
     </row>
     <row r="37" ht="20.05" customHeight="1">
       <c r="A37" s="10">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s" s="11">
         <v>12</v>
       </c>
       <c r="C37" t="s" s="12">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="D37" s="13">
         <v>1</v>
       </c>
       <c r="E37" t="s" s="12">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F37" t="s" s="12">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s" s="12">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H37" t="s" s="12">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="I37" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="13" cm="1">
         <f t="array" ref="J37">I37*D37</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="13" cm="1">
         <f t="array" ref="K37">SUMIF(B37,"LS",J37)</f>
@@ -4476,46 +4984,48 @@
       </c>
       <c r="L37" s="13" cm="1">
         <f t="array" ref="L37">SUMIF(B37,"C2",J37)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="13" cm="1">
         <f t="array" ref="M37">SUMIF(B37,"P2",J37)</f>
         <v>0</v>
       </c>
-      <c r="N37" s="14"/>
+      <c r="N37" t="s" s="12">
+        <v>82</v>
+      </c>
       <c r="O37" s="14"/>
     </row>
     <row r="38" ht="20.05" customHeight="1">
       <c r="A38" s="10">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s" s="12">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="D38" s="13">
         <v>1</v>
       </c>
       <c r="E38" t="s" s="12">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F38" t="s" s="12">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G38" t="s" s="12">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H38" t="s" s="12">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="I38" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="13" cm="1">
         <f t="array" ref="J38">I38*D38</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="13" cm="1">
         <f t="array" ref="K38">SUMIF(B38,"LS",J38)</f>
@@ -4527,35 +5037,37 @@
       </c>
       <c r="M38" s="13" cm="1">
         <f t="array" ref="M38">SUMIF(B38,"P2",J38)</f>
-        <v>1</v>
-      </c>
-      <c r="N38" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="N38" t="s" s="12">
+        <v>82</v>
+      </c>
       <c r="O38" s="14"/>
     </row>
     <row r="39" ht="20.05" customHeight="1">
       <c r="A39" s="10">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s" s="12">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="D39" s="13">
         <v>1</v>
       </c>
       <c r="E39" t="s" s="12">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F39" t="s" s="12">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G39" t="s" s="12">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="H39" t="s" s="12">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="I39" s="13">
         <v>0</v>
@@ -4577,34 +5089,34 @@
         <v>0</v>
       </c>
       <c r="N39" t="s" s="12">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="O39" s="14"/>
     </row>
     <row r="40" ht="20.05" customHeight="1">
       <c r="A40" s="10">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s" s="11">
         <v>12</v>
       </c>
       <c r="C40" t="s" s="12">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D40" s="13">
         <v>1</v>
       </c>
       <c r="E40" t="s" s="12">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F40" t="s" s="12">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G40" t="s" s="12">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="H40" t="s" s="12">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="I40" s="13">
         <v>0</v>
@@ -4626,34 +5138,34 @@
         <v>0</v>
       </c>
       <c r="N40" t="s" s="12">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="O40" s="14"/>
     </row>
     <row r="41" ht="20.05" customHeight="1">
       <c r="A41" s="10">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s" s="11">
         <v>12</v>
       </c>
       <c r="C41" t="s" s="12">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D41" s="13">
         <v>1</v>
       </c>
       <c r="E41" t="s" s="12">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F41" t="s" s="12">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s" s="12">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="H41" t="s" s="12">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="I41" s="13">
         <v>0</v>
@@ -4675,41 +5187,42 @@
         <v>0</v>
       </c>
       <c r="N41" t="s" s="12">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="O41" s="14"/>
     </row>
     <row r="42" ht="20.05" customHeight="1">
       <c r="A42" s="10">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s" s="12">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D42" s="13">
         <v>1</v>
       </c>
       <c r="E42" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F42" t="s" s="12">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="G42" t="s" s="12">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="12">
-        <v>69</v>
-      </c>
-      <c r="I42" s="13">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="I42" s="13" cm="1">
+        <f t="array" ref="I42">33/1000</f>
+        <v>0.033</v>
       </c>
       <c r="J42" s="13" cm="1">
         <f t="array" ref="J42">I42*D42</f>
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="K42" s="13" cm="1">
         <f t="array" ref="K42">SUMIF(B42,"LS",J42)</f>
@@ -4721,44 +5234,46 @@
       </c>
       <c r="M42" s="13" cm="1">
         <f t="array" ref="M42">SUMIF(B42,"P2",J42)</f>
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="N42" t="s" s="12">
-        <v>72</v>
-      </c>
-      <c r="O42" s="14"/>
+        <v>96</v>
+      </c>
+      <c r="O42" t="s" s="12">
+        <v>97</v>
+      </c>
     </row>
     <row r="43" ht="20.05" customHeight="1">
       <c r="A43" s="10">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s" s="12">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="D43" s="13">
         <v>1</v>
       </c>
       <c r="E43" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F43" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G43" t="s" s="12">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="H43" t="s" s="12">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="I43" s="13">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J43" s="13" cm="1">
         <f t="array" ref="J43">I43*D43</f>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K43" s="13" cm="1">
         <f t="array" ref="K43">SUMIF(B43,"LS",J43)</f>
@@ -4770,44 +5285,42 @@
       </c>
       <c r="M43" s="13" cm="1">
         <f t="array" ref="M43">SUMIF(B43,"P2",J43)</f>
-        <v>0</v>
-      </c>
-      <c r="N43" t="s" s="12">
-        <v>72</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="N43" s="14"/>
       <c r="O43" s="14"/>
     </row>
     <row r="44" ht="20.05" customHeight="1">
       <c r="A44" s="10">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s" s="12">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D44" s="13">
         <v>1</v>
       </c>
       <c r="E44" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F44" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G44" t="s" s="12">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="H44" t="s" s="12">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I44" s="13">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="J44" s="13" cm="1">
         <f t="array" ref="J44">I44*D44</f>
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="K44" s="13" cm="1">
         <f t="array" ref="K44">SUMIF(B44,"LS",J44)</f>
@@ -4819,44 +5332,42 @@
       </c>
       <c r="M44" s="13" cm="1">
         <f t="array" ref="M44">SUMIF(B44,"P2",J44)</f>
-        <v>0</v>
-      </c>
-      <c r="N44" t="s" s="12">
-        <v>77</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="N44" s="14"/>
       <c r="O44" s="14"/>
     </row>
     <row r="45" ht="20.05" customHeight="1">
       <c r="A45" s="10">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s" s="12">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D45" s="13">
         <v>1</v>
       </c>
       <c r="E45" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F45" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="H45" t="s" s="12">
-        <v>69</v>
+        <v>19</v>
+      </c>
+      <c r="H45" s="13">
+        <v>392</v>
       </c>
       <c r="I45" s="13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J45" s="13" cm="1">
         <f t="array" ref="J45">I45*D45</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K45" s="13" cm="1">
         <f t="array" ref="K45">SUMIF(B45,"LS",J45)</f>
@@ -4868,44 +5379,44 @@
       </c>
       <c r="M45" s="13" cm="1">
         <f t="array" ref="M45">SUMIF(B45,"P2",J45)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N45" t="s" s="12">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O45" s="14"/>
     </row>
     <row r="46" ht="20.05" customHeight="1">
       <c r="A46" s="10">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s" s="11">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s" s="12">
+        <v>75</v>
+      </c>
+      <c r="D46" s="13">
         <v>12</v>
       </c>
-      <c r="C46" t="s" s="12">
-        <v>79</v>
-      </c>
-      <c r="D46" s="13">
-        <v>1</v>
-      </c>
       <c r="E46" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F46" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="H46" t="s" s="12">
-        <v>69</v>
+        <v>19</v>
+      </c>
+      <c r="H46" s="13">
+        <v>392</v>
       </c>
       <c r="I46" s="13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J46" s="13" cm="1">
         <f t="array" ref="J46">I46*D46</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="K46" s="13" cm="1">
         <f t="array" ref="K46">SUMIF(B46,"LS",J46)</f>
@@ -4917,44 +5428,44 @@
       </c>
       <c r="M46" s="13" cm="1">
         <f t="array" ref="M46">SUMIF(B46,"P2",J46)</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N46" t="s" s="12">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O46" s="14"/>
     </row>
     <row r="47" ht="20.05" customHeight="1">
       <c r="A47" s="10">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s" s="12">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D47" s="13">
         <v>1</v>
       </c>
       <c r="E47" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F47" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G47" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="H47" t="s" s="12">
-        <v>69</v>
+        <v>19</v>
+      </c>
+      <c r="H47" s="13">
+        <v>392</v>
       </c>
       <c r="I47" s="13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J47" s="13" cm="1">
         <f t="array" ref="J47">I47*D47</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K47" s="13" cm="1">
         <f t="array" ref="K47">SUMIF(B47,"LS",J47)</f>
@@ -4966,44 +5477,44 @@
       </c>
       <c r="M47" s="13" cm="1">
         <f t="array" ref="M47">SUMIF(B47,"P2",J47)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N47" t="s" s="12">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O47" s="14"/>
     </row>
     <row r="48" ht="20.05" customHeight="1">
       <c r="A48" s="10">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s" s="12">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D48" s="13">
         <v>1</v>
       </c>
       <c r="E48" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F48" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G48" t="s" s="12">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="H48" t="s" s="12">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="I48" s="13">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J48" s="13" cm="1">
         <f t="array" ref="J48">I48*D48</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K48" s="13" cm="1">
         <f t="array" ref="K48">SUMIF(B48,"LS",J48)</f>
@@ -5015,44 +5526,42 @@
       </c>
       <c r="M48" s="13" cm="1">
         <f t="array" ref="M48">SUMIF(B48,"P2",J48)</f>
-        <v>0</v>
-      </c>
-      <c r="N48" t="s" s="12">
-        <v>72</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="N48" s="14"/>
       <c r="O48" s="14"/>
     </row>
     <row r="49" ht="20.05" customHeight="1">
       <c r="A49" s="10">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s" s="12">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="D49" s="13">
         <v>1</v>
       </c>
       <c r="E49" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F49" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s" s="12">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H49" t="s" s="12">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="I49" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="13" cm="1">
         <f t="array" ref="J49">I49*D49</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="13" cm="1">
         <f t="array" ref="K49">SUMIF(B49,"LS",J49)</f>
@@ -5064,44 +5573,44 @@
       </c>
       <c r="M49" s="13" cm="1">
         <f t="array" ref="M49">SUMIF(B49,"P2",J49)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="s" s="12">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="O49" s="14"/>
     </row>
     <row r="50" ht="20.05" customHeight="1">
       <c r="A50" s="10">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s" s="11">
         <v>13</v>
       </c>
       <c r="C50" t="s" s="12">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D50" s="13">
         <v>1</v>
       </c>
       <c r="E50" t="s" s="12">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F50" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="H50" t="s" s="12">
-        <v>69</v>
+        <v>19</v>
+      </c>
+      <c r="H50" s="13">
+        <v>4698</v>
       </c>
       <c r="I50" s="13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J50" s="13" cm="1">
         <f t="array" ref="J50">I50*D50</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K50" s="13" cm="1">
         <f t="array" ref="K50">SUMIF(B50,"LS",J50)</f>
@@ -5113,44 +5622,42 @@
       </c>
       <c r="M50" s="13" cm="1">
         <f t="array" ref="M50">SUMIF(B50,"P2",J50)</f>
-        <v>0</v>
-      </c>
-      <c r="N50" t="s" s="12">
-        <v>70</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N50" s="14"/>
       <c r="O50" s="14"/>
     </row>
     <row r="51" ht="20.05" customHeight="1">
       <c r="A51" s="10">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s" s="11">
         <v>13</v>
       </c>
       <c r="C51" t="s" s="12">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="D51" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="s" s="12">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F51" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G51" t="s" s="12">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="H51" t="s" s="12">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="I51" s="13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J51" s="13" cm="1">
         <f t="array" ref="J51">I51*D51</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K51" s="13" cm="1">
         <f t="array" ref="K51">SUMIF(B51,"LS",J51)</f>
@@ -5162,44 +5669,42 @@
       </c>
       <c r="M51" s="13" cm="1">
         <f t="array" ref="M51">SUMIF(B51,"P2",J51)</f>
-        <v>0</v>
-      </c>
-      <c r="N51" t="s" s="12">
-        <v>72</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="N51" s="14"/>
       <c r="O51" s="14"/>
     </row>
     <row r="52" ht="20.05" customHeight="1">
       <c r="A52" s="10">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s" s="11">
         <v>13</v>
       </c>
       <c r="C52" t="s" s="12">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="D52" s="13">
         <v>1</v>
       </c>
       <c r="E52" t="s" s="12">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F52" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G52" t="s" s="12">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="H52" t="s" s="12">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I52" s="13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J52" s="13" cm="1">
         <f t="array" ref="J52">I52*D52</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K52" s="13" cm="1">
         <f t="array" ref="K52">SUMIF(B52,"LS",J52)</f>
@@ -5211,44 +5716,42 @@
       </c>
       <c r="M52" s="13" cm="1">
         <f t="array" ref="M52">SUMIF(B52,"P2",J52)</f>
-        <v>0</v>
-      </c>
-      <c r="N52" t="s" s="12">
-        <v>72</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="N52" s="14"/>
       <c r="O52" s="14"/>
     </row>
     <row r="53" ht="20.05" customHeight="1">
       <c r="A53" s="10">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s" s="11">
         <v>13</v>
       </c>
       <c r="C53" t="s" s="12">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="D53" s="13">
         <v>1</v>
       </c>
       <c r="E53" t="s" s="12">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F53" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G53" t="s" s="12">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="H53" t="s" s="12">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I53" s="13">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="J53" s="13" cm="1">
         <f t="array" ref="J53">I53*D53</f>
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="K53" s="13" cm="1">
         <f t="array" ref="K53">SUMIF(B53,"LS",J53)</f>
@@ -5260,44 +5763,42 @@
       </c>
       <c r="M53" s="13" cm="1">
         <f t="array" ref="M53">SUMIF(B53,"P2",J53)</f>
-        <v>0</v>
-      </c>
-      <c r="N53" t="s" s="12">
-        <v>72</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="N53" s="14"/>
       <c r="O53" s="14"/>
     </row>
     <row r="54" ht="20.05" customHeight="1">
       <c r="A54" s="10">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s" s="11">
         <v>13</v>
       </c>
       <c r="C54" t="s" s="12">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D54" s="13">
         <v>1</v>
       </c>
       <c r="E54" t="s" s="12">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F54" t="s" s="12">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="G54" t="s" s="12">
         <v>68</v>
       </c>
       <c r="H54" t="s" s="12">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="I54" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="13" cm="1">
         <f t="array" ref="J54">I54*D54</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" s="13" cm="1">
         <f t="array" ref="K54">SUMIF(B54,"LS",J54)</f>
@@ -5309,37 +5810,35 @@
       </c>
       <c r="M54" s="13" cm="1">
         <f t="array" ref="M54">SUMIF(B54,"P2",J54)</f>
-        <v>0</v>
-      </c>
-      <c r="N54" t="s" s="12">
-        <v>88</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N54" s="14"/>
       <c r="O54" s="14"/>
     </row>
     <row r="55" ht="20.05" customHeight="1">
       <c r="A55" s="10">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s" s="12">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="D55" s="13">
         <v>1</v>
       </c>
       <c r="E55" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F55" t="s" s="12">
         <v>18</v>
       </c>
       <c r="G55" t="s" s="12">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="H55" t="s" s="12">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="I55" s="13">
         <v>3.5</v>
@@ -5354,48 +5853,48 @@
       </c>
       <c r="L55" s="13" cm="1">
         <f t="array" ref="L55">SUMIF(B55,"C2",J55)</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M55" s="13" cm="1">
         <f t="array" ref="M55">SUMIF(B55,"P2",J55)</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N55" t="s" s="12">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="O55" s="14"/>
     </row>
     <row r="56" ht="20.05" customHeight="1">
       <c r="A56" s="10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s" s="11">
         <v>13</v>
       </c>
       <c r="C56" t="s" s="12">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D56" s="13">
         <v>1</v>
       </c>
       <c r="E56" t="s" s="12">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F56" t="s" s="12">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s" s="12">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="H56" t="s" s="12">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="I56" s="13">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J56" s="13" cm="1">
         <f t="array" ref="J56">I56*D56</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K56" s="13" cm="1">
         <f t="array" ref="K56">SUMIF(B56,"LS",J56)</f>
@@ -5407,44 +5906,44 @@
       </c>
       <c r="M56" s="13" cm="1">
         <f t="array" ref="M56">SUMIF(B56,"P2",J56)</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N56" t="s" s="12">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="O56" s="14"/>
     </row>
     <row r="57" ht="20.05" customHeight="1">
       <c r="A57" s="10">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s" s="12">
+        <v>103</v>
+      </c>
+      <c r="D57" s="13">
+        <v>1</v>
+      </c>
+      <c r="E57" t="s" s="12">
         <v>93</v>
       </c>
-      <c r="D57" s="13">
-        <v>1</v>
-      </c>
-      <c r="E57" t="s" s="12">
-        <v>21</v>
-      </c>
       <c r="F57" t="s" s="12">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G57" t="s" s="12">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="H57" t="s" s="12">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="I57" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="13" cm="1">
         <f t="array" ref="J57">I57*D57</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" s="13" cm="1">
         <f t="array" ref="K57">SUMIF(B57,"LS",J57)</f>
@@ -5452,48 +5951,48 @@
       </c>
       <c r="L57" s="13" cm="1">
         <f t="array" ref="L57">SUMIF(B57,"C2",J57)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="13" cm="1">
         <f t="array" ref="M57">SUMIF(B57,"P2",J57)</f>
         <v>0</v>
       </c>
       <c r="N57" t="s" s="12">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O57" s="14"/>
     </row>
     <row r="58" ht="20.05" customHeight="1">
       <c r="A58" s="10">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s" s="11">
         <v>13</v>
       </c>
       <c r="C58" t="s" s="12">
+        <v>104</v>
+      </c>
+      <c r="D58" s="13">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s" s="12">
         <v>93</v>
       </c>
-      <c r="D58" s="13">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s" s="12">
-        <v>22</v>
-      </c>
       <c r="F58" t="s" s="12">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G58" t="s" s="12">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="H58" t="s" s="12">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="I58" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="13" cm="1">
         <f t="array" ref="J58">I58*D58</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" s="13" cm="1">
         <f t="array" ref="K58">SUMIF(B58,"LS",J58)</f>
@@ -5505,45 +6004,44 @@
       </c>
       <c r="M58" s="13" cm="1">
         <f t="array" ref="M58">SUMIF(B58,"P2",J58)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="s" s="12">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O58" s="14"/>
     </row>
     <row r="59" ht="20.05" customHeight="1">
       <c r="A59" s="10">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s" s="12">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D59" s="13">
         <v>1</v>
       </c>
       <c r="E59" t="s" s="12">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F59" t="s" s="12">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="G59" t="s" s="12">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="H59" t="s" s="12">
-        <v>99</v>
-      </c>
-      <c r="I59" s="13" cm="1">
-        <f t="array" ref="I59">30/100</f>
-        <v>0.3</v>
+        <v>44</v>
+      </c>
+      <c r="I59" s="13">
+        <v>0</v>
       </c>
       <c r="J59" s="13" cm="1">
         <f t="array" ref="J59">I59*D59</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K59" s="13" cm="1">
         <f t="array" ref="K59">SUMIF(B59,"LS",J59)</f>
@@ -5551,51 +6049,48 @@
       </c>
       <c r="L59" s="13" cm="1">
         <f t="array" ref="L59">SUMIF(B59,"C2",J59)</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M59" s="13" cm="1">
         <f t="array" ref="M59">SUMIF(B59,"P2",J59)</f>
         <v>0</v>
       </c>
       <c r="N59" t="s" s="12">
-        <v>100</v>
-      </c>
-      <c r="O59" t="s" s="12">
-        <v>101</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="O59" s="14"/>
     </row>
     <row r="60" ht="20.25" customHeight="1">
       <c r="A60" s="15">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s" s="16">
         <v>13</v>
       </c>
       <c r="C60" t="s" s="17">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D60" s="18">
         <v>1</v>
       </c>
       <c r="E60" t="s" s="17">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F60" t="s" s="17">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="G60" t="s" s="17">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="H60" t="s" s="17">
-        <v>104</v>
-      </c>
-      <c r="I60" s="18" cm="1">
-        <f t="array" ref="I60">33/1000</f>
-        <v>0.033</v>
+        <v>44</v>
+      </c>
+      <c r="I60" s="18">
+        <v>0</v>
       </c>
       <c r="J60" s="18" cm="1">
         <f t="array" ref="J60">I60*D60</f>
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="K60" s="18" cm="1">
         <f t="array" ref="K60">SUMIF(B60,"LS",J60)</f>
@@ -5607,130 +6102,1462 @@
       </c>
       <c r="M60" s="18" cm="1">
         <f t="array" ref="M60">SUMIF(B60,"P2",J60)</f>
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="N60" t="s" s="17">
-        <v>105</v>
-      </c>
-      <c r="O60" t="s" s="17">
-        <v>106</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="O60" s="19"/>
     </row>
     <row r="61" ht="20.25" customHeight="1">
-      <c r="A61" s="19"/>
-      <c r="B61" s="19"/>
-      <c r="C61" t="s" s="20">
-        <v>107</v>
-      </c>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="21" cm="1">
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
+      <c r="C61" t="s" s="21">
+        <v>108</v>
+      </c>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="22" cm="1">
         <f t="array" ref="J61">ROUNDUP(SUM(J3:J60),0)</f>
         <v>158</v>
       </c>
-      <c r="K61" s="21" cm="1">
+      <c r="K61" s="22" cm="1">
         <f t="array" ref="K61">ROUNDUP(SUM(K3:K60),0)</f>
         <v>47</v>
       </c>
-      <c r="L61" s="21" cm="1">
+      <c r="L61" s="22" cm="1">
         <f t="array" ref="L61">ROUNDUP(SUM(L3:L60),0)</f>
         <v>60</v>
       </c>
-      <c r="M61" s="21" cm="1">
+      <c r="M61" s="22" cm="1">
         <f t="array" ref="M61">ROUNDUP(SUM(M3:M60),0)</f>
         <v>53</v>
       </c>
-      <c r="N61" s="19"/>
-      <c r="O61" s="19"/>
+      <c r="N61" s="20"/>
+      <c r="O61" s="20"/>
     </row>
     <row r="62" ht="20.05" customHeight="1">
-      <c r="A62" s="22"/>
-      <c r="B62" t="s" s="23">
+      <c r="A62" s="23"/>
+      <c r="B62" t="s" s="24">
         <v>12</v>
       </c>
-      <c r="C62" t="s" s="23">
-        <v>108</v>
-      </c>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="24" cm="1">
+      <c r="C62" t="s" s="24">
+        <v>109</v>
+      </c>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="23"/>
+      <c r="I62" s="23"/>
+      <c r="J62" s="25" cm="1">
         <f t="array" ref="J62">K$61+L$61</f>
         <v>107</v>
       </c>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="22"/>
-      <c r="N62" s="22"/>
-      <c r="O62" s="22"/>
+      <c r="K62" s="23"/>
+      <c r="L62" s="23"/>
+      <c r="M62" s="23"/>
+      <c r="N62" s="23"/>
+      <c r="O62" s="23"/>
     </row>
     <row r="63" ht="20.05" customHeight="1">
-      <c r="A63" s="22"/>
-      <c r="B63" t="s" s="23">
+      <c r="A63" s="23"/>
+      <c r="B63" t="s" s="24">
         <v>13</v>
       </c>
-      <c r="C63" t="s" s="23">
-        <v>109</v>
-      </c>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="24" cm="1">
+      <c r="C63" t="s" s="24">
+        <v>110</v>
+      </c>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="23"/>
+      <c r="J63" s="25" cm="1">
         <f t="array" ref="J63">K$61+M$61</f>
         <v>100</v>
       </c>
-      <c r="K63" s="22"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="22"/>
-      <c r="N63" s="22"/>
-      <c r="O63" s="22"/>
+      <c r="K63" s="23"/>
+      <c r="L63" s="23"/>
+      <c r="M63" s="23"/>
+      <c r="N63" s="23"/>
+      <c r="O63" s="23"/>
     </row>
     <row r="64" ht="20.05" customHeight="1">
-      <c r="A64" s="22"/>
-      <c r="B64" t="s" s="23">
-        <v>110</v>
-      </c>
-      <c r="C64" t="s" s="23">
+      <c r="A64" s="23"/>
+      <c r="B64" t="s" s="24">
         <v>111</v>
       </c>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22"/>
-      <c r="J64" s="24" cm="1">
+      <c r="C64" t="s" s="24">
+        <v>112</v>
+      </c>
+      <c r="D64" s="23"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="23"/>
+      <c r="I64" s="23"/>
+      <c r="J64" s="25" cm="1">
         <f t="array" ref="J64">J$61</f>
         <v>158</v>
       </c>
-      <c r="K64" s="22"/>
-      <c r="L64" s="22"/>
-      <c r="M64" s="22"/>
-      <c r="N64" s="22"/>
-      <c r="O64" s="22"/>
+      <c r="K64" s="23"/>
+      <c r="L64" s="23"/>
+      <c r="M64" s="23"/>
+      <c r="N64" s="23"/>
+      <c r="O64" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="N55" r:id="rId1" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=3100234"/>
-    <hyperlink ref="N56" r:id="rId2" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=3100234"/>
-    <hyperlink ref="N57" r:id="rId3" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=200009"/>
-    <hyperlink ref="N58" r:id="rId4" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=200009"/>
-    <hyperlink ref="N59" r:id="rId5" location="" tooltip="" display="https://www.thomassci.com/p/spectrophotometer-cuvettes?q=1180W05"/>
-    <hyperlink ref="N60" r:id="rId6" location="" tooltip="" display="https://www.fishersci.com/shop/products/costar-pcr-tubes-3/07200681#?keyword=pcr"/>
+    <hyperlink ref="N17" r:id="rId1" location="" tooltip="" display="https://www.thomassci.com/p/spectrophotometer-cuvettes?q=1180W05"/>
+    <hyperlink ref="N19" r:id="rId2" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=200009"/>
+    <hyperlink ref="N21" r:id="rId3" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=3100234"/>
+    <hyperlink ref="N24" r:id="rId4" location="" tooltip="" display="https://www.mouser.com/ProductDetail/ams-OSRAM/GC-VJLPL1.13-KQKS-V2V3-1?qs=QpmGXVUTftHD6Ze6bLOUKg=="/>
+    <hyperlink ref="N42" r:id="rId5" location="" tooltip="" display="https://www.fishersci.com/shop/products/costar-pcr-tubes-3/07200681#?keyword=pcr"/>
+    <hyperlink ref="N49" r:id="rId6" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=200009"/>
+    <hyperlink ref="N55" r:id="rId7" location="" tooltip="" display="https://www.proto-advantage.com/store/product_info.php?products_id=3100234"/>
   </hyperlinks>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E15"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="8.10156" style="73" customWidth="1"/>
+    <col min="2" max="2" width="32.6719" style="73" customWidth="1"/>
+    <col min="3" max="3" width="23.6719" style="73" customWidth="1"/>
+    <col min="4" max="4" width="24.625" style="73" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="73" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="73" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" t="s" s="28">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>160</v>
+      </c>
+      <c r="C2" t="s" s="3">
+        <v>161</v>
+      </c>
+      <c r="D2" t="s" s="3">
+        <v>162</v>
+      </c>
+      <c r="E2" t="s" s="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" s="29">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s" s="6">
+        <v>165</v>
+      </c>
+      <c r="C3" t="s" s="7">
+        <v>253</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" t="s" s="7">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" s="30">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s" s="11">
+        <v>311</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" t="s" s="12">
+        <v>312</v>
+      </c>
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" s="30">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s" s="11">
+        <v>313</v>
+      </c>
+      <c r="C5" t="s" s="12">
+        <v>314</v>
+      </c>
+      <c r="D5" t="s" s="12">
+        <v>315</v>
+      </c>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" s="30">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s" s="11">
+        <v>316</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+    </row>
+    <row r="7" ht="20.05" customHeight="1">
+      <c r="A7" s="30">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s" s="11">
+        <v>317</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" t="s" s="12">
+        <v>318</v>
+      </c>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" ht="20.05" customHeight="1">
+      <c r="A8" s="30">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s" s="11">
+        <v>319</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" t="s" s="12">
+        <v>320</v>
+      </c>
+      <c r="E8" s="14"/>
+    </row>
+    <row r="9" ht="20.05" customHeight="1">
+      <c r="A9" s="30">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s" s="11">
+        <v>321</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" t="s" s="12">
+        <v>322</v>
+      </c>
+      <c r="E9" s="14"/>
+    </row>
+    <row r="10" ht="20.05" customHeight="1">
+      <c r="A10" s="30">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s" s="11">
+        <v>210</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" t="s" s="12">
+        <v>323</v>
+      </c>
+      <c r="E10" t="s" s="49">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" ht="20.05" customHeight="1">
+      <c r="A11" s="30">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s" s="11">
+        <v>324</v>
+      </c>
+      <c r="C11" t="s" s="12">
+        <v>184</v>
+      </c>
+      <c r="D11" t="s" s="12">
+        <v>325</v>
+      </c>
+      <c r="E11" t="s" s="52">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" ht="20.05" customHeight="1">
+      <c r="A12" s="30">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s" s="11">
+        <v>326</v>
+      </c>
+      <c r="C12" t="s" s="12">
+        <v>184</v>
+      </c>
+      <c r="D12" t="s" s="12">
+        <v>327</v>
+      </c>
+      <c r="E12" t="s" s="72">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" ht="20.05" customHeight="1">
+      <c r="A13" s="30">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s" s="11">
+        <v>222</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+    </row>
+    <row r="14" ht="20.05" customHeight="1">
+      <c r="A14" s="31"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+    </row>
+    <row r="15" ht="20.05" customHeight="1">
+      <c r="A15" s="31"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E13"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="5" width="16.3516" style="74" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="74" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" t="s" s="3">
+        <v>329</v>
+      </c>
+      <c r="C2" t="s" s="3">
+        <v>330</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" t="s" s="75">
+        <v>331</v>
+      </c>
+      <c r="B3" s="76"/>
+      <c r="C3" s="8">
+        <v>100</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" t="s" s="77">
+        <v>332</v>
+      </c>
+      <c r="B4" t="s" s="11">
+        <v>333</v>
+      </c>
+      <c r="C4" s="13">
+        <v>700</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" t="s" s="77">
+        <v>334</v>
+      </c>
+      <c r="B5" t="s" s="11">
+        <v>333</v>
+      </c>
+      <c r="C5" s="13" cm="1">
+        <f t="array" ref="C5">C4/C3</f>
+        <v>7</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" t="s" s="77">
+        <v>335</v>
+      </c>
+      <c r="B6" t="s" s="11">
+        <v>336</v>
+      </c>
+      <c r="C6" s="13">
+        <v>50</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+    </row>
+    <row r="7" ht="20.05" customHeight="1">
+      <c r="A7" t="s" s="77">
+        <v>337</v>
+      </c>
+      <c r="B7" t="s" s="11">
+        <v>338</v>
+      </c>
+      <c r="C7" s="13">
+        <v>0.7</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" ht="20.05" customHeight="1">
+      <c r="A8" t="s" s="77">
+        <v>339</v>
+      </c>
+      <c r="B8" t="s" s="11">
+        <v>338</v>
+      </c>
+      <c r="C8" s="13" cm="1">
+        <f t="array" ref="C8">(C5*C6)/1000+C7</f>
+        <v>1.05</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+    </row>
+    <row r="9" ht="20.05" customHeight="1">
+      <c r="A9" t="s" s="77">
+        <v>340</v>
+      </c>
+      <c r="B9" t="s" s="11">
+        <v>338</v>
+      </c>
+      <c r="C9" s="13">
+        <v>3.3</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+    </row>
+    <row r="10" ht="20.05" customHeight="1">
+      <c r="A10" t="s" s="77">
+        <v>341</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="13" cm="1">
+        <f t="array" ref="C10">ROUND(C8/C9,1)</f>
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+    </row>
+    <row r="11" ht="20.05" customHeight="1">
+      <c r="A11" t="s" s="77">
+        <v>342</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="13">
+        <v>65535</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+    </row>
+    <row r="12" ht="20.05" customHeight="1">
+      <c r="A12" t="s" s="77">
+        <v>343</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="13" cm="1">
+        <f t="array" ref="C12">C11*C10</f>
+        <v>19660.5</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+    </row>
+    <row r="13" ht="20.05" customHeight="1">
+      <c r="A13" t="s" s="77">
+        <v>344</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="13">
+        <v>20000</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F66"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="8.21094" style="78" customWidth="1"/>
+    <col min="2" max="2" width="38.5" style="78" customWidth="1"/>
+    <col min="3" max="3" width="24.8516" style="78" customWidth="1"/>
+    <col min="4" max="4" width="16.3516" style="78" customWidth="1"/>
+    <col min="5" max="6" width="27.3359" style="78" customWidth="1"/>
+    <col min="7" max="16384" width="16.3516" style="78" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.25" customHeight="1">
+      <c r="A1" t="s" s="28">
+        <v>113</v>
+      </c>
+      <c r="B1" t="s" s="3">
+        <v>345</v>
+      </c>
+      <c r="C1" t="s" s="3">
+        <v>346</v>
+      </c>
+      <c r="D1" t="s" s="3">
+        <v>347</v>
+      </c>
+      <c r="E1" t="s" s="3">
+        <v>348</v>
+      </c>
+      <c r="F1" t="s" s="3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" s="29">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s" s="79">
+        <v>349</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" ht="20.05" customHeight="1">
+      <c r="A3" s="30">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s" s="11">
+        <v>350</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" s="30">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s" s="11">
+        <v>352</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" s="30">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s" s="11">
+        <v>353</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" s="30">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s" s="11">
+        <v>354</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+    </row>
+    <row r="7" ht="20.05" customHeight="1">
+      <c r="A7" s="30">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s" s="11">
+        <v>355</v>
+      </c>
+      <c r="C7" t="s" s="12">
+        <v>356</v>
+      </c>
+      <c r="D7" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+    </row>
+    <row r="8" ht="20.05" customHeight="1">
+      <c r="A8" s="30">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s" s="11">
+        <v>357</v>
+      </c>
+      <c r="C8" t="s" s="12">
+        <v>358</v>
+      </c>
+      <c r="D8" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+    </row>
+    <row r="9" ht="20.05" customHeight="1">
+      <c r="A9" s="30">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s" s="11">
+        <v>359</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+    </row>
+    <row r="10" ht="20.05" customHeight="1">
+      <c r="A10" s="30">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s" s="11">
+        <v>360</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" ht="20.05" customHeight="1">
+      <c r="A11" s="30">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s" s="11">
+        <v>361</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" ht="20.05" customHeight="1">
+      <c r="A12" s="30">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s" s="11">
+        <v>362</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+    </row>
+    <row r="13" ht="20.05" customHeight="1">
+      <c r="A13" s="30">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s" s="11">
+        <v>363</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+    </row>
+    <row r="14" ht="20.05" customHeight="1">
+      <c r="A14" s="30">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s" s="11">
+        <v>364</v>
+      </c>
+      <c r="C14" t="s" s="12">
+        <v>365</v>
+      </c>
+      <c r="D14" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" ht="20.05" customHeight="1">
+      <c r="A15" s="30">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s" s="11">
+        <v>366</v>
+      </c>
+      <c r="C15" t="s" s="12">
+        <v>367</v>
+      </c>
+      <c r="D15" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" ht="20.05" customHeight="1">
+      <c r="A16" s="30">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="11">
+        <v>368</v>
+      </c>
+      <c r="C16" t="s" s="12">
+        <v>369</v>
+      </c>
+      <c r="D16" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" ht="20.05" customHeight="1">
+      <c r="A17" s="30">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s" s="11">
+        <v>370</v>
+      </c>
+      <c r="C17" t="s" s="12">
+        <v>371</v>
+      </c>
+      <c r="D17" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E17" t="s" s="12">
+        <v>372</v>
+      </c>
+      <c r="F17" t="s" s="12">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="18" ht="20.05" customHeight="1">
+      <c r="A18" s="30">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s" s="11">
+        <v>374</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="19" ht="20.05" customHeight="1">
+      <c r="A19" s="30">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s" s="11">
+        <v>375</v>
+      </c>
+      <c r="C19" t="s" s="12">
+        <v>376</v>
+      </c>
+      <c r="D19" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" ht="20.05" customHeight="1">
+      <c r="A20" s="30">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s" s="11">
+        <v>377</v>
+      </c>
+      <c r="C20" t="s" s="12">
+        <v>378</v>
+      </c>
+      <c r="D20" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+    </row>
+    <row r="21" ht="20.05" customHeight="1">
+      <c r="A21" s="30">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s" s="11">
+        <v>379</v>
+      </c>
+      <c r="C21" t="s" s="12">
+        <v>380</v>
+      </c>
+      <c r="D21" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+    </row>
+    <row r="22" ht="20.05" customHeight="1">
+      <c r="A22" s="30">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s" s="11">
+        <v>381</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+    </row>
+    <row r="23" ht="20.05" customHeight="1">
+      <c r="A23" s="30">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s" s="11">
+        <v>382</v>
+      </c>
+      <c r="C23" t="s" s="12">
+        <v>367</v>
+      </c>
+      <c r="D23" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+    </row>
+    <row r="24" ht="20.05" customHeight="1">
+      <c r="A24" s="30">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s" s="11">
+        <v>383</v>
+      </c>
+      <c r="C24" t="s" s="12">
+        <v>369</v>
+      </c>
+      <c r="D24" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+    </row>
+    <row r="25" ht="20.05" customHeight="1">
+      <c r="A25" s="30">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s" s="11">
+        <v>384</v>
+      </c>
+      <c r="C25" t="s" s="12">
+        <v>385</v>
+      </c>
+      <c r="D25" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" ht="20.05" customHeight="1">
+      <c r="A26" s="30">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s" s="11">
+        <v>386</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+    </row>
+    <row r="27" ht="20.05" customHeight="1">
+      <c r="A27" s="30">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s" s="11">
+        <v>387</v>
+      </c>
+      <c r="C27" t="s" s="12">
+        <v>367</v>
+      </c>
+      <c r="D27" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+    </row>
+    <row r="28" ht="20.05" customHeight="1">
+      <c r="A28" s="30">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s" s="11">
+        <v>388</v>
+      </c>
+      <c r="C28" t="s" s="12">
+        <v>369</v>
+      </c>
+      <c r="D28" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+    </row>
+    <row r="29" ht="20.05" customHeight="1">
+      <c r="A29" s="30">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s" s="11">
+        <v>389</v>
+      </c>
+      <c r="C29" t="s" s="12">
+        <v>390</v>
+      </c>
+      <c r="D29" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+    </row>
+    <row r="30" ht="20.05" customHeight="1">
+      <c r="A30" s="30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s" s="11">
+        <v>391</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+    </row>
+    <row r="31" ht="20.05" customHeight="1">
+      <c r="A31" s="30">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s" s="11">
+        <v>392</v>
+      </c>
+      <c r="C31" t="s" s="12">
+        <v>367</v>
+      </c>
+      <c r="D31" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+    </row>
+    <row r="32" ht="20.05" customHeight="1">
+      <c r="A32" s="30">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s" s="11">
+        <v>393</v>
+      </c>
+      <c r="C32" t="s" s="12">
+        <v>369</v>
+      </c>
+      <c r="D32" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+    </row>
+    <row r="33" ht="20.05" customHeight="1">
+      <c r="A33" s="30">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s" s="11">
+        <v>394</v>
+      </c>
+      <c r="C33" t="s" s="12">
+        <v>395</v>
+      </c>
+      <c r="D33" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+    </row>
+    <row r="34" ht="20.05" customHeight="1">
+      <c r="A34" s="30">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s" s="11">
+        <v>396</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+    </row>
+    <row r="35" ht="20.05" customHeight="1">
+      <c r="A35" s="30">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s" s="11">
+        <v>397</v>
+      </c>
+      <c r="C35" t="s" s="12">
+        <v>367</v>
+      </c>
+      <c r="D35" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+    </row>
+    <row r="36" ht="20.05" customHeight="1">
+      <c r="A36" s="30">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s" s="11">
+        <v>398</v>
+      </c>
+      <c r="C36" t="s" s="12">
+        <v>369</v>
+      </c>
+      <c r="D36" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+    </row>
+    <row r="37" ht="20.05" customHeight="1">
+      <c r="A37" s="30">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s" s="11">
+        <v>399</v>
+      </c>
+      <c r="C37" t="s" s="12">
+        <v>400</v>
+      </c>
+      <c r="D37" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+    </row>
+    <row r="38" ht="20.05" customHeight="1">
+      <c r="A38" s="30">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s" s="11">
+        <v>401</v>
+      </c>
+      <c r="C38" s="14"/>
+      <c r="D38" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+    </row>
+    <row r="39" ht="20.05" customHeight="1">
+      <c r="A39" s="30">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s" s="11">
+        <v>402</v>
+      </c>
+      <c r="C39" s="14"/>
+      <c r="D39" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+    </row>
+    <row r="40" ht="20.05" customHeight="1">
+      <c r="A40" s="30">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s" s="11">
+        <v>403</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" t="s" s="12">
+        <v>404</v>
+      </c>
+      <c r="E40" t="s" s="12">
+        <v>405</v>
+      </c>
+      <c r="F40" s="14"/>
+    </row>
+    <row r="41" ht="20.05" customHeight="1">
+      <c r="A41" s="30">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s" s="11">
+        <v>406</v>
+      </c>
+      <c r="C41" s="14"/>
+      <c r="D41" t="s" s="12">
+        <v>404</v>
+      </c>
+      <c r="E41" t="s" s="12">
+        <v>405</v>
+      </c>
+      <c r="F41" s="14"/>
+    </row>
+    <row r="42" ht="20.05" customHeight="1">
+      <c r="A42" s="30">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s" s="11">
+        <v>407</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" t="s" s="12">
+        <v>404</v>
+      </c>
+      <c r="E42" t="s" s="12">
+        <v>405</v>
+      </c>
+      <c r="F42" s="14"/>
+    </row>
+    <row r="43" ht="20.05" customHeight="1">
+      <c r="A43" s="30">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s" s="11">
+        <v>408</v>
+      </c>
+      <c r="C43" s="14"/>
+      <c r="D43" t="s" s="12">
+        <v>404</v>
+      </c>
+      <c r="E43" t="s" s="12">
+        <v>405</v>
+      </c>
+      <c r="F43" s="14"/>
+    </row>
+    <row r="44" ht="20.05" customHeight="1">
+      <c r="A44" s="30">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s" s="11">
+        <v>409</v>
+      </c>
+      <c r="C44" s="14"/>
+      <c r="D44" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+    </row>
+    <row r="45" ht="20.05" customHeight="1">
+      <c r="A45" s="30">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s" s="11">
+        <v>410</v>
+      </c>
+      <c r="C45" s="14"/>
+      <c r="D45" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+    </row>
+    <row r="46" ht="20.05" customHeight="1">
+      <c r="A46" s="30">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s" s="11">
+        <v>411</v>
+      </c>
+      <c r="C46" s="14"/>
+      <c r="D46" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+    </row>
+    <row r="47" ht="20.05" customHeight="1">
+      <c r="A47" s="30">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s" s="11">
+        <v>412</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+    </row>
+    <row r="48" ht="20.05" customHeight="1">
+      <c r="A48" s="30">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s" s="11">
+        <v>413</v>
+      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+    </row>
+    <row r="49" ht="20.05" customHeight="1">
+      <c r="A49" s="30">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s" s="11">
+        <v>414</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" t="s" s="12">
+        <v>126</v>
+      </c>
+      <c r="E49" t="s" s="12">
+        <v>405</v>
+      </c>
+      <c r="F49" s="14"/>
+    </row>
+    <row r="50" ht="20.05" customHeight="1">
+      <c r="A50" s="31"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+    </row>
+    <row r="51" ht="20.05" customHeight="1">
+      <c r="A51" s="31"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+    </row>
+    <row r="52" ht="20.05" customHeight="1">
+      <c r="A52" s="30">
+        <v>100</v>
+      </c>
+      <c r="B52" t="s" s="80">
+        <v>415</v>
+      </c>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+    </row>
+    <row r="53" ht="20.05" customHeight="1">
+      <c r="A53" s="30">
+        <v>101</v>
+      </c>
+      <c r="B53" t="s" s="11">
+        <v>416</v>
+      </c>
+      <c r="C53" s="14"/>
+      <c r="D53" t="s" s="12">
+        <v>351</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+    </row>
+    <row r="54" ht="20.05" customHeight="1">
+      <c r="A54" s="31"/>
+      <c r="B54" t="s" s="11">
+        <v>417</v>
+      </c>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+    </row>
+    <row r="55" ht="20.05" customHeight="1">
+      <c r="A55" s="31"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+    </row>
+    <row r="56" ht="20.05" customHeight="1">
+      <c r="A56" s="31"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+    </row>
+    <row r="57" ht="20.05" customHeight="1">
+      <c r="A57" s="31"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+    </row>
+    <row r="58" ht="20.05" customHeight="1">
+      <c r="A58" s="31"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+    </row>
+    <row r="59" ht="20.05" customHeight="1">
+      <c r="A59" s="31"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+    </row>
+    <row r="60" ht="20.05" customHeight="1">
+      <c r="A60" s="31"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+    </row>
+    <row r="61" ht="20.05" customHeight="1">
+      <c r="A61" s="31"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+    </row>
+    <row r="62" ht="20.05" customHeight="1">
+      <c r="A62" s="31"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+    </row>
+    <row r="63" ht="20.05" customHeight="1">
+      <c r="A63" s="30">
+        <v>1000</v>
+      </c>
+      <c r="B63" t="s" s="80">
+        <v>418</v>
+      </c>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+    </row>
+    <row r="64" ht="20.05" customHeight="1">
+      <c r="A64" s="30">
+        <v>1001</v>
+      </c>
+      <c r="B64" t="s" s="11">
+        <v>419</v>
+      </c>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+    </row>
+    <row r="65" ht="20.05" customHeight="1">
+      <c r="A65" s="30">
+        <v>1002</v>
+      </c>
+      <c r="B65" t="s" s="11">
+        <v>420</v>
+      </c>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+    </row>
+    <row r="66" ht="20.05" customHeight="1">
+      <c r="A66" s="31"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+    </row>
+  </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
@@ -5747,25 +7574,25 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="4.85156" style="25" customWidth="1"/>
-    <col min="2" max="2" width="6.35156" style="25" customWidth="1"/>
-    <col min="3" max="3" width="33.4141" style="25" customWidth="1"/>
-    <col min="4" max="4" width="16.3516" style="25" customWidth="1"/>
-    <col min="5" max="16384" width="16.3516" style="25" customWidth="1"/>
+    <col min="1" max="1" width="4.85156" style="26" customWidth="1"/>
+    <col min="2" max="2" width="6.35156" style="26" customWidth="1"/>
+    <col min="3" max="3" width="33.4141" style="26" customWidth="1"/>
+    <col min="4" max="4" width="16.3516" style="26" customWidth="1"/>
+    <col min="5" max="16384" width="16.3516" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B1" t="s" s="3">
         <v>2</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" ht="20.25" customHeight="1">
@@ -5776,10 +7603,10 @@
         <v>15</v>
       </c>
       <c r="C2" t="s" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" ht="20.05" customHeight="1">
@@ -5787,13 +7614,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="11">
+        <v>118</v>
+      </c>
+      <c r="C3" t="s" s="12">
+        <v>119</v>
+      </c>
+      <c r="D3" t="s" s="12">
         <v>117</v>
-      </c>
-      <c r="C3" t="s" s="12">
-        <v>118</v>
-      </c>
-      <c r="D3" t="s" s="12">
-        <v>116</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
@@ -5801,13 +7628,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="11">
+        <v>118</v>
+      </c>
+      <c r="C4" t="s" s="12">
+        <v>120</v>
+      </c>
+      <c r="D4" t="s" s="12">
         <v>117</v>
-      </c>
-      <c r="C4" t="s" s="12">
-        <v>119</v>
-      </c>
-      <c r="D4" t="s" s="12">
-        <v>116</v>
       </c>
     </row>
     <row r="5" ht="20.05" customHeight="1">
@@ -5815,13 +7642,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="11">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s" s="12">
+        <v>121</v>
+      </c>
+      <c r="D5" t="s" s="12">
         <v>117</v>
-      </c>
-      <c r="C5" t="s" s="12">
-        <v>120</v>
-      </c>
-      <c r="D5" t="s" s="12">
-        <v>116</v>
       </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
@@ -5829,13 +7656,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="11">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s" s="12">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s" s="12">
         <v>117</v>
-      </c>
-      <c r="C6" t="s" s="12">
-        <v>121</v>
-      </c>
-      <c r="D6" t="s" s="12">
-        <v>116</v>
       </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
@@ -5843,13 +7670,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="11">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s" s="12">
+        <v>123</v>
+      </c>
+      <c r="D7" t="s" s="12">
         <v>117</v>
-      </c>
-      <c r="C7" t="s" s="12">
-        <v>122</v>
-      </c>
-      <c r="D7" t="s" s="12">
-        <v>116</v>
       </c>
     </row>
     <row r="8" ht="20.05" customHeight="1">
@@ -5857,13 +7684,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="11">
+        <v>118</v>
+      </c>
+      <c r="C8" t="s" s="12">
+        <v>124</v>
+      </c>
+      <c r="D8" t="s" s="12">
         <v>117</v>
-      </c>
-      <c r="C8" t="s" s="12">
-        <v>123</v>
-      </c>
-      <c r="D8" t="s" s="12">
-        <v>116</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
@@ -5871,13 +7698,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="11">
+        <v>118</v>
+      </c>
+      <c r="C9" t="s" s="12">
+        <v>125</v>
+      </c>
+      <c r="D9" t="s" s="12">
         <v>117</v>
-      </c>
-      <c r="C9" t="s" s="12">
-        <v>124</v>
-      </c>
-      <c r="D9" t="s" s="12">
-        <v>116</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
@@ -5885,13 +7712,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s" s="12">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s" s="12">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" ht="20.05" customHeight="1">
@@ -5899,13 +7726,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="11">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" t="s" s="12">
+        <v>127</v>
+      </c>
+      <c r="D11" t="s" s="12">
         <v>126</v>
-      </c>
-      <c r="D11" t="s" s="12">
-        <v>125</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
@@ -5913,13 +7740,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="11">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s" s="12">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s" s="12">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
@@ -5927,13 +7754,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="11">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s" s="12">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s" s="12">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" ht="20.05" customHeight="1">
@@ -5941,13 +7768,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="11">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s" s="12">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s" s="12">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" ht="20.05" customHeight="1">
@@ -5955,13 +7782,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="11">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C15" t="s" s="12">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D15" t="s" s="12">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" ht="20.05" customHeight="1">
@@ -5969,13 +7796,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="11">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s" s="12">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s" s="12">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -5989,22 +7816,352 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:G25"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E30"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="26" customWidth="1"/>
-    <col min="2" max="2" width="30.6719" style="26" customWidth="1"/>
-    <col min="3" max="3" width="23.6719" style="26" customWidth="1"/>
-    <col min="4" max="4" width="61.1719" style="26" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="26" customWidth="1"/>
-    <col min="6" max="6" width="11.7812" style="26" customWidth="1"/>
-    <col min="7" max="7" width="38.4531" style="26" customWidth="1"/>
-    <col min="8" max="16384" width="16.3516" style="26" customWidth="1"/>
+    <col min="1" max="1" width="8.10938" style="27" customWidth="1"/>
+    <col min="2" max="2" width="45.6094" style="27" customWidth="1"/>
+    <col min="3" max="5" width="16.3516" style="27" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" t="s" s="28">
+        <v>135</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" s="29">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s" s="6">
+        <v>136</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" s="30">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s" s="11">
+        <v>137</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" ht="20.05" customHeight="1">
+      <c r="A5" s="30">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s" s="11">
+        <v>138</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" ht="20.05" customHeight="1">
+      <c r="A6" s="30">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s" s="11">
+        <v>139</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+    </row>
+    <row r="7" ht="20.05" customHeight="1">
+      <c r="A7" s="30">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s" s="11">
+        <v>140</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" ht="32.05" customHeight="1">
+      <c r="A8" s="30">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s" s="11">
+        <v>141</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+    </row>
+    <row r="9" ht="20.05" customHeight="1">
+      <c r="A9" s="30">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s" s="11">
+        <v>142</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+    </row>
+    <row r="10" ht="32.05" customHeight="1">
+      <c r="A10" s="30">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s" s="11">
+        <v>143</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+    </row>
+    <row r="11" ht="44.05" customHeight="1">
+      <c r="A11" s="30">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s" s="11">
+        <v>144</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+    </row>
+    <row r="12" ht="44.05" customHeight="1">
+      <c r="A12" s="30">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s" s="11">
+        <v>145</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+    </row>
+    <row r="13" ht="44.1" customHeight="1">
+      <c r="A13" s="30">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s" s="11">
+        <v>146</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+    </row>
+    <row r="14" ht="32.05" customHeight="1">
+      <c r="A14" s="30">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s" s="11">
+        <v>147</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1">
+      <c r="A15" s="30">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s" s="11">
+        <v>148</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" ht="20.05" customHeight="1">
+      <c r="A16" s="30">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="11">
+        <v>149</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+    </row>
+    <row r="17" ht="44.05" customHeight="1">
+      <c r="A17" s="30">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s" s="11">
+        <v>150</v>
+      </c>
+      <c r="C17" t="s" s="12">
+        <v>151</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" ht="20.05" customHeight="1">
+      <c r="A18" s="30">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s" s="11">
+        <v>152</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+    </row>
+    <row r="19" ht="20.05" customHeight="1">
+      <c r="A19" s="30">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s" s="11">
+        <v>153</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+    </row>
+    <row r="20" ht="20.05" customHeight="1">
+      <c r="A20" s="30">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s" s="11">
+        <v>154</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+    </row>
+    <row r="21" ht="20.05" customHeight="1">
+      <c r="A21" s="30">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s" s="11">
+        <v>155</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" ht="20.05" customHeight="1">
+      <c r="A22" s="30">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s" s="11">
+        <v>156</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+    </row>
+    <row r="23" ht="20.05" customHeight="1">
+      <c r="A23" s="30">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s" s="11">
+        <v>157</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" ht="20.05" customHeight="1">
+      <c r="A24" s="30">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s" s="11">
+        <v>158</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+    </row>
+    <row r="25" ht="20.05" customHeight="1">
+      <c r="A25" s="31"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+    </row>
+    <row r="26" ht="20.05" customHeight="1">
+      <c r="A26" s="31"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+    </row>
+    <row r="27" ht="20.05" customHeight="1">
+      <c r="A27" s="31"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+    </row>
+    <row r="28" ht="20.05" customHeight="1">
+      <c r="A28" s="31"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+    </row>
+    <row r="29" ht="20.05" customHeight="1">
+      <c r="A29" s="31"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+    </row>
+    <row r="30" ht="20.05" customHeight="1">
+      <c r="A30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A2:G25"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="8.10156" style="33" customWidth="1"/>
+    <col min="2" max="2" width="30.6719" style="33" customWidth="1"/>
+    <col min="3" max="3" width="23.6719" style="33" customWidth="1"/>
+    <col min="4" max="4" width="61.1719" style="33" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="33" customWidth="1"/>
+    <col min="6" max="6" width="11.7812" style="33" customWidth="1"/>
+    <col min="7" max="7" width="38.4531" style="33" customWidth="1"/>
+    <col min="8" max="16384" width="16.3516" style="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="2">
+        <v>159</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6014,39 +8171,39 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" t="s" s="27">
-        <v>134</v>
+      <c r="A2" t="s" s="28">
+        <v>135</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" t="s" s="3">
-        <v>139</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="28">
+      <c r="A3" s="29">
         <v>1</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s" s="7">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" t="s" s="7">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="F3" t="b" s="8">
         <v>0</v>
@@ -6054,15 +8211,15 @@
       <c r="G3" s="7"/>
     </row>
     <row r="4" ht="20.05" customHeight="1">
-      <c r="A4" s="29">
+      <c r="A4" s="30">
         <v>2</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" t="s" s="12">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="E4" s="14"/>
       <c r="F4" t="b" s="13">
@@ -6071,17 +8228,17 @@
       <c r="G4" s="12"/>
     </row>
     <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" s="29">
+      <c r="A5" s="30">
         <v>3</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s" s="12">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s" s="12">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" t="b" s="13">
@@ -6090,38 +8247,38 @@
       <c r="G5" s="12"/>
     </row>
     <row r="6" ht="32.05" customHeight="1">
-      <c r="A6" s="29">
+      <c r="A6" s="30">
         <v>4</v>
       </c>
       <c r="B6" t="s" s="11">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s" s="12">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s" s="12">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" t="b" s="13">
         <v>1</v>
       </c>
       <c r="G6" t="s" s="12">
-        <v>151</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="29">
+      <c r="A7" s="30">
         <v>5</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s" s="12">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s" s="12">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" t="b" s="13">
@@ -6130,17 +8287,17 @@
       <c r="G7" s="12"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="29">
+      <c r="A8" s="30">
         <v>6</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C8" t="s" s="12">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s" s="12">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" t="b" s="13">
@@ -6149,38 +8306,38 @@
       <c r="G8" s="12"/>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="29">
+      <c r="A9" s="30">
         <v>7</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s" s="12">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="D9" t="s" s="12">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" t="b" s="13">
         <v>1</v>
       </c>
       <c r="G9" t="s" s="12">
-        <v>161</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="29">
+      <c r="A10" s="30">
         <v>8</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s" s="12">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="D10" t="s" s="12">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" t="b" s="13">
@@ -6189,17 +8346,17 @@
       <c r="G10" s="12"/>
     </row>
     <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="29">
+      <c r="A11" s="30">
         <v>9</v>
       </c>
       <c r="B11" t="s" s="11">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s" s="12">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="D11" t="s" s="12">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" t="b" s="13">
@@ -6208,17 +8365,17 @@
       <c r="G11" s="12"/>
     </row>
     <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="29">
+      <c r="A12" s="30">
         <v>10</v>
       </c>
       <c r="B12" t="s" s="11">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C12" t="s" s="12">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s" s="12">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" t="b" s="13">
@@ -6227,56 +8384,56 @@
       <c r="G12" s="12"/>
     </row>
     <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="29">
+      <c r="A13" s="30">
         <v>11</v>
       </c>
       <c r="B13" t="s" s="11">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" t="s" s="12">
-        <v>171</v>
-      </c>
-      <c r="E13" t="s" s="30">
-        <v>172</v>
-      </c>
-      <c r="F13" t="b" s="31">
-        <v>1</v>
-      </c>
-      <c r="G13" s="32"/>
+        <v>196</v>
+      </c>
+      <c r="E13" t="s" s="34">
+        <v>197</v>
+      </c>
+      <c r="F13" t="b" s="35">
+        <v>1</v>
+      </c>
+      <c r="G13" s="36"/>
     </row>
     <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="29">
+      <c r="A14" s="30">
         <v>12</v>
       </c>
       <c r="B14" t="s" s="11">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="C14" s="14"/>
-      <c r="D14" t="s" s="33">
-        <v>174</v>
-      </c>
-      <c r="E14" t="s" s="34">
-        <v>175</v>
-      </c>
-      <c r="F14" t="b" s="35">
-        <v>1</v>
-      </c>
-      <c r="G14" s="36"/>
+      <c r="D14" t="s" s="37">
+        <v>199</v>
+      </c>
+      <c r="E14" t="s" s="38">
+        <v>200</v>
+      </c>
+      <c r="F14" t="b" s="39">
+        <v>1</v>
+      </c>
+      <c r="G14" s="40"/>
     </row>
     <row r="15" ht="20.85" customHeight="1">
-      <c r="A15" s="29">
+      <c r="A15" s="30">
         <v>13</v>
       </c>
       <c r="B15" t="s" s="11">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" t="s" s="12">
-        <v>177</v>
-      </c>
-      <c r="E15" t="s" s="37">
-        <v>178</v>
+        <v>202</v>
+      </c>
+      <c r="E15" t="s" s="41">
+        <v>203</v>
       </c>
       <c r="F15" t="b" s="13">
         <v>1</v>
@@ -6284,125 +8441,125 @@
       <c r="G15" s="12"/>
     </row>
     <row r="16" ht="21.7" customHeight="1">
-      <c r="A16" s="29">
+      <c r="A16" s="30">
         <v>14</v>
       </c>
       <c r="B16" t="s" s="11">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C16" s="14"/>
-      <c r="D16" t="s" s="38">
-        <v>180</v>
-      </c>
-      <c r="E16" t="s" s="39">
-        <v>181</v>
-      </c>
-      <c r="F16" t="b" s="40">
-        <v>1</v>
-      </c>
-      <c r="G16" s="41"/>
+      <c r="D16" t="s" s="42">
+        <v>205</v>
+      </c>
+      <c r="E16" t="s" s="43">
+        <v>206</v>
+      </c>
+      <c r="F16" t="b" s="44">
+        <v>1</v>
+      </c>
+      <c r="G16" s="45"/>
     </row>
     <row r="17" ht="20.85" customHeight="1">
-      <c r="A17" s="29">
+      <c r="A17" s="30">
         <v>15</v>
       </c>
       <c r="B17" t="s" s="11">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" t="s" s="12">
-        <v>183</v>
-      </c>
-      <c r="E17" t="s" s="42">
-        <v>184</v>
-      </c>
-      <c r="F17" t="b" s="43">
-        <v>1</v>
-      </c>
-      <c r="G17" s="44"/>
+        <v>208</v>
+      </c>
+      <c r="E17" t="s" s="46">
+        <v>209</v>
+      </c>
+      <c r="F17" t="b" s="47">
+        <v>1</v>
+      </c>
+      <c r="G17" s="48"/>
     </row>
     <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="29">
+      <c r="A18" s="30">
         <v>16</v>
       </c>
       <c r="B18" t="s" s="11">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" t="s" s="12">
-        <v>186</v>
-      </c>
-      <c r="E18" t="s" s="45">
-        <v>187</v>
-      </c>
-      <c r="F18" t="b" s="46">
-        <v>1</v>
-      </c>
-      <c r="G18" s="47"/>
+        <v>211</v>
+      </c>
+      <c r="E18" t="s" s="49">
+        <v>212</v>
+      </c>
+      <c r="F18" t="b" s="50">
+        <v>1</v>
+      </c>
+      <c r="G18" s="51"/>
     </row>
     <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="29">
+      <c r="A19" s="30">
         <v>17</v>
       </c>
       <c r="B19" t="s" s="11">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" t="s" s="12">
-        <v>189</v>
-      </c>
-      <c r="E19" t="s" s="48">
-        <v>190</v>
-      </c>
-      <c r="F19" t="b" s="46">
-        <v>1</v>
-      </c>
-      <c r="G19" s="47"/>
+        <v>214</v>
+      </c>
+      <c r="E19" t="s" s="52">
+        <v>215</v>
+      </c>
+      <c r="F19" t="b" s="50">
+        <v>1</v>
+      </c>
+      <c r="G19" s="51"/>
     </row>
     <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="29">
+      <c r="A20" s="30">
         <v>18</v>
       </c>
       <c r="B20" t="s" s="11">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" t="s" s="12">
-        <v>192</v>
-      </c>
-      <c r="E20" t="s" s="49">
-        <v>193</v>
-      </c>
-      <c r="F20" t="b" s="50">
-        <v>1</v>
-      </c>
-      <c r="G20" s="51"/>
+        <v>217</v>
+      </c>
+      <c r="E20" t="s" s="53">
+        <v>218</v>
+      </c>
+      <c r="F20" t="b" s="54">
+        <v>1</v>
+      </c>
+      <c r="G20" s="55"/>
     </row>
     <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" s="29">
+      <c r="A21" s="30">
         <v>19</v>
       </c>
       <c r="B21" t="s" s="11">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C21" s="14"/>
-      <c r="D21" t="s" s="33">
-        <v>195</v>
-      </c>
-      <c r="E21" t="s" s="52">
-        <v>196</v>
-      </c>
-      <c r="F21" t="b" s="35">
-        <v>1</v>
-      </c>
-      <c r="G21" s="36"/>
+      <c r="D21" t="s" s="37">
+        <v>220</v>
+      </c>
+      <c r="E21" t="s" s="56">
+        <v>221</v>
+      </c>
+      <c r="F21" t="b" s="39">
+        <v>1</v>
+      </c>
+      <c r="G21" s="40"/>
     </row>
     <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" s="29">
+      <c r="A22" s="30">
         <v>20</v>
       </c>
       <c r="B22" t="s" s="11">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
@@ -6413,15 +8570,15 @@
       <c r="G22" s="12"/>
     </row>
     <row r="23" ht="20.05" customHeight="1">
-      <c r="A23" s="29">
+      <c r="A23" s="30">
         <v>21</v>
       </c>
       <c r="B23" t="s" s="11">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" t="s" s="12">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" t="b" s="13">
@@ -6430,15 +8587,15 @@
       <c r="G23" s="12"/>
     </row>
     <row r="24" ht="20.05" customHeight="1">
-      <c r="A24" s="29">
+      <c r="A24" s="30">
         <v>22</v>
       </c>
       <c r="B24" t="s" s="11">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" t="s" s="12">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" t="b" s="13">
@@ -6447,8 +8604,8 @@
       <c r="G24" s="12"/>
     </row>
     <row r="25" ht="20.05" customHeight="1">
-      <c r="A25" s="53"/>
-      <c r="B25" s="54"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="32"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
@@ -6467,356 +8624,58 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E20"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="8.10156" style="55" customWidth="1"/>
-    <col min="2" max="2" width="43.5" style="55" customWidth="1"/>
-    <col min="3" max="3" width="34.2656" style="55" customWidth="1"/>
-    <col min="4" max="4" width="34.5" style="55" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="55" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27.65" customHeight="1">
-      <c r="A1" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" t="s" s="27">
-        <v>134</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>135</v>
-      </c>
-      <c r="C2" t="s" s="3">
-        <v>136</v>
-      </c>
-      <c r="D2" t="s" s="3">
-        <v>137</v>
-      </c>
-      <c r="E2" t="s" s="3">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="28">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s" s="6">
-        <v>140</v>
-      </c>
-      <c r="C3" t="s" s="7">
-        <v>203</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" t="s" s="7">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" ht="20.05" customHeight="1">
-      <c r="A4" s="29">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s" s="11">
-        <v>205</v>
-      </c>
-      <c r="C4" t="s" s="12">
-        <v>206</v>
-      </c>
-      <c r="D4" t="s" s="12">
-        <v>207</v>
-      </c>
-      <c r="E4" s="14"/>
-    </row>
-    <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" s="29">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s" s="11">
-        <v>208</v>
-      </c>
-      <c r="C5" t="s" s="12">
-        <v>209</v>
-      </c>
-      <c r="D5" t="s" s="12">
-        <v>210</v>
-      </c>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="29">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s" s="11">
-        <v>211</v>
-      </c>
-      <c r="C6" t="s" s="12">
-        <v>212</v>
-      </c>
-      <c r="D6" t="s" s="12">
-        <v>213</v>
-      </c>
-      <c r="E6" s="14"/>
-    </row>
-    <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="29">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s" s="11">
-        <v>214</v>
-      </c>
-      <c r="C7" t="s" s="12">
-        <v>215</v>
-      </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-    </row>
-    <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="29">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s" s="11">
-        <v>170</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" t="s" s="12">
-        <v>216</v>
-      </c>
-      <c r="E8" t="s" s="30">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="29">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s" s="11">
-        <v>173</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" t="s" s="33">
-        <v>217</v>
-      </c>
-      <c r="E9" t="s" s="34">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" ht="20.85" customHeight="1">
-      <c r="A10" s="29">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s" s="11">
-        <v>176</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" t="s" s="12">
-        <v>218</v>
-      </c>
-      <c r="E10" t="s" s="37">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" ht="21.7" customHeight="1">
-      <c r="A11" s="29">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s" s="11">
-        <v>179</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" t="s" s="38">
-        <v>219</v>
-      </c>
-      <c r="E11" t="s" s="39">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" ht="20.85" customHeight="1">
-      <c r="A12" s="29">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s" s="11">
-        <v>182</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" t="s" s="12">
-        <v>220</v>
-      </c>
-      <c r="E12" t="s" s="42">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="29">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s" s="11">
-        <v>185</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" t="s" s="12">
-        <v>221</v>
-      </c>
-      <c r="E13" t="s" s="45">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="29">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s" s="11">
-        <v>188</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" t="s" s="12">
-        <v>222</v>
-      </c>
-      <c r="E14" t="s" s="48">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="29">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s" s="11">
-        <v>191</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" t="s" s="12">
-        <v>223</v>
-      </c>
-      <c r="E15" t="s" s="49">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="29">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s" s="11">
-        <v>194</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" t="s" s="33">
-        <v>224</v>
-      </c>
-      <c r="E16" t="s" s="52">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="29">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s" s="11">
-        <v>225</v>
-      </c>
-      <c r="C17" t="s" s="12">
-        <v>226</v>
-      </c>
-      <c r="D17" t="s" s="12">
-        <v>227</v>
-      </c>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="29">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s" s="11">
-        <v>197</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-    </row>
-    <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="53"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
-  <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E9"/>
+  <dimension ref="A2:F20"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="56" customWidth="1"/>
-    <col min="2" max="2" width="54.8516" style="56" customWidth="1"/>
-    <col min="3" max="3" width="23.6719" style="56" customWidth="1"/>
-    <col min="4" max="4" width="26.3516" style="56" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="56" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="56" customWidth="1"/>
+    <col min="1" max="1" width="8.10156" style="57" customWidth="1"/>
+    <col min="2" max="2" width="45" style="57" customWidth="1"/>
+    <col min="3" max="3" width="37.8438" style="57" customWidth="1"/>
+    <col min="4" max="4" width="34.5" style="57" customWidth="1"/>
+    <col min="5" max="6" width="16.3516" style="57" customWidth="1"/>
+    <col min="7" max="16384" width="16.3516" style="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" t="s" s="27">
-        <v>134</v>
+      <c r="A2" t="s" s="28">
+        <v>135</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>138</v>
+        <v>163</v>
+      </c>
+      <c r="F2" t="s" s="3">
+        <v>228</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="28">
+      <c r="A3" s="29">
         <v>1</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s" s="7">
         <v>229</v>
@@ -6825,94 +8684,289 @@
       <c r="E3" t="s" s="7">
         <v>230</v>
       </c>
+      <c r="F3" t="b" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
-      <c r="A4" s="29">
+      <c r="A4" s="30">
         <v>2</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>143</v>
-      </c>
-      <c r="C4" s="14"/>
+        <v>231</v>
+      </c>
+      <c r="C4" t="s" s="12">
+        <v>232</v>
+      </c>
       <c r="D4" t="s" s="12">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E4" s="14"/>
+      <c r="F4" t="b" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" s="29">
+      <c r="A5" s="30">
         <v>3</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C5" t="s" s="12">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D5" t="s" s="12">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E5" s="14"/>
+      <c r="F5" t="b" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="29">
+      <c r="A6" s="30">
         <v>4</v>
       </c>
       <c r="B6" t="s" s="11">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C6" t="s" s="12">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D6" t="s" s="12">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E6" s="14"/>
+      <c r="F6" t="b" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="29">
+      <c r="A7" s="30">
         <v>5</v>
       </c>
-      <c r="B7" t="s" s="11">
-        <v>238</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" t="s" s="12">
-        <v>239</v>
-      </c>
-      <c r="E7" t="s" s="57">
-        <v>187</v>
+      <c r="B7" t="s" s="58">
+        <v>240</v>
+      </c>
+      <c r="C7" t="s" s="59">
+        <v>241</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" t="b" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="29">
-        <v>7</v>
+      <c r="A8" s="30">
+        <v>6</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" t="s" s="12">
-        <v>241</v>
-      </c>
-      <c r="E8" t="s" s="58">
-        <v>184</v>
+        <v>242</v>
+      </c>
+      <c r="E8" t="s" s="34">
+        <v>197</v>
+      </c>
+      <c r="F8" t="b" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="29">
+      <c r="A9" s="30">
         <v>7</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="D9" t="s" s="37">
+        <v>243</v>
+      </c>
+      <c r="E9" t="s" s="38">
+        <v>200</v>
+      </c>
+      <c r="F9" t="b" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="20.85" customHeight="1">
+      <c r="A10" s="30">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s" s="11">
+        <v>201</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" t="s" s="12">
+        <v>244</v>
+      </c>
+      <c r="E10" t="s" s="41">
+        <v>203</v>
+      </c>
+      <c r="F10" t="b" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="21.7" customHeight="1">
+      <c r="A11" s="30">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s" s="11">
+        <v>204</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" t="s" s="42">
+        <v>245</v>
+      </c>
+      <c r="E11" t="s" s="43">
+        <v>206</v>
+      </c>
+      <c r="F11" t="b" s="61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="20.85" customHeight="1">
+      <c r="A12" s="30">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s" s="11">
+        <v>207</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" t="s" s="12">
+        <v>246</v>
+      </c>
+      <c r="E12" t="s" s="46">
+        <v>209</v>
+      </c>
+      <c r="F12" t="b" s="62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="20.05" customHeight="1">
+      <c r="A13" s="30">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s" s="11">
+        <v>210</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" t="s" s="12">
+        <v>247</v>
+      </c>
+      <c r="E13" t="s" s="49">
+        <v>212</v>
+      </c>
+      <c r="F13" t="b" s="62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="20.05" customHeight="1">
+      <c r="A14" s="30">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s" s="11">
+        <v>213</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" t="s" s="12">
+        <v>248</v>
+      </c>
+      <c r="E14" t="s" s="52">
+        <v>215</v>
+      </c>
+      <c r="F14" t="b" s="62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="20.05" customHeight="1">
+      <c r="A15" s="30">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s" s="11">
+        <v>216</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" t="s" s="12">
+        <v>249</v>
+      </c>
+      <c r="E15" t="s" s="53">
+        <v>218</v>
+      </c>
+      <c r="F15" t="b" s="62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="20.05" customHeight="1">
+      <c r="A16" s="30">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="11">
+        <v>219</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" t="s" s="37">
+        <v>250</v>
+      </c>
+      <c r="E16" t="s" s="56">
+        <v>221</v>
+      </c>
+      <c r="F16" t="b" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="20.05" customHeight="1">
+      <c r="A17" s="30">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s" s="11">
+        <v>251</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" t="b" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="20.05" customHeight="1">
+      <c r="A18" s="30">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s" s="11">
+        <v>222</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" t="b" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="20.05" customHeight="1">
+      <c r="A19" s="31"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" ht="20.05" customHeight="1">
+      <c r="A20" s="31"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -6927,256 +8981,170 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E18"/>
+  <dimension ref="A2:F9"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="59" customWidth="1"/>
-    <col min="2" max="2" width="56.1172" style="59" customWidth="1"/>
-    <col min="3" max="3" width="23.6719" style="59" customWidth="1"/>
-    <col min="4" max="4" width="47.2422" style="59" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="59" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="59" customWidth="1"/>
+    <col min="1" max="1" width="8.10156" style="63" customWidth="1"/>
+    <col min="2" max="2" width="54.8516" style="63" customWidth="1"/>
+    <col min="3" max="3" width="23.6719" style="63" customWidth="1"/>
+    <col min="4" max="4" width="26.3516" style="63" customWidth="1"/>
+    <col min="5" max="6" width="16.3516" style="63" customWidth="1"/>
+    <col min="7" max="16384" width="16.3516" style="63" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" t="s" s="27">
-        <v>134</v>
+      <c r="A2" t="s" s="28">
+        <v>135</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>138</v>
+        <v>163</v>
+      </c>
+      <c r="F2" t="s" s="3">
+        <v>228</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="28">
+      <c r="A3" s="29">
         <v>1</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s" s="7">
-        <v>203</v>
+        <v>253</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" t="s" s="7">
-        <v>204</v>
+        <v>254</v>
+      </c>
+      <c r="F3" t="b" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
-      <c r="A4" s="29">
+      <c r="A4" s="30">
         <v>2</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" t="s" s="12">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E4" s="14"/>
+      <c r="F4" t="b" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" s="29">
+      <c r="A5" s="30">
         <v>3</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s" s="12">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D5" t="s" s="12">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E5" s="14"/>
+      <c r="F5" t="b" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="29">
+      <c r="A6" s="30">
         <v>4</v>
       </c>
       <c r="B6" t="s" s="11">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C6" t="s" s="12">
-        <v>248</v>
-      </c>
-      <c r="D6" s="14"/>
+        <v>260</v>
+      </c>
+      <c r="D6" t="s" s="12">
+        <v>261</v>
+      </c>
       <c r="E6" s="14"/>
+      <c r="F6" t="b" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="29">
+      <c r="A7" s="30">
         <v>5</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" t="s" s="12">
-        <v>250</v>
-      </c>
-      <c r="E7" s="14"/>
+        <v>263</v>
+      </c>
+      <c r="E7" t="s" s="64">
+        <v>212</v>
+      </c>
+      <c r="F7" t="b" s="62">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="29">
-        <v>6</v>
+      <c r="A8" s="30">
+        <v>7</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="D8" t="s" s="12">
+        <v>265</v>
+      </c>
+      <c r="E8" t="s" s="65">
+        <v>209</v>
+      </c>
+      <c r="F8" t="b" s="62">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="29">
+      <c r="A9" s="30">
         <v>7</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>252</v>
-      </c>
-      <c r="C9" t="s" s="12">
-        <v>253</v>
-      </c>
-      <c r="D9" t="s" s="12">
-        <v>254</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
       <c r="E9" s="14"/>
-    </row>
-    <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="29">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s" s="11">
-        <v>255</v>
-      </c>
-      <c r="C10" t="s" s="12">
-        <v>256</v>
-      </c>
-      <c r="D10" t="s" s="12">
-        <v>257</v>
-      </c>
-      <c r="E10" s="60"/>
-    </row>
-    <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="29">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s" s="11">
-        <v>258</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" t="s" s="12">
-        <v>259</v>
-      </c>
-      <c r="E11" t="s" s="58">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="29">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s" s="11">
-        <v>185</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" t="s" s="12">
-        <v>260</v>
-      </c>
-      <c r="E12" t="s" s="45">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="29">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s" s="11">
-        <v>188</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" t="s" s="12">
-        <v>261</v>
-      </c>
-      <c r="E13" t="s" s="48">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="29">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s" s="11">
-        <v>191</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" t="s" s="12">
-        <v>262</v>
-      </c>
-      <c r="E14" t="s" s="49">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="29">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s" s="11">
-        <v>194</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" t="s" s="33">
-        <v>263</v>
-      </c>
-      <c r="E15" t="s" s="52">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="29">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s" s="11">
-        <v>197</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
+      <c r="F9" t="b" s="13">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -7191,92 +9159,257 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A2:E18"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.3516" style="61" customWidth="1"/>
-    <col min="2" max="2" width="35.1484" style="61" customWidth="1"/>
-    <col min="3" max="5" width="16.3516" style="61" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="61" customWidth="1"/>
+    <col min="1" max="1" width="8.10156" style="66" customWidth="1"/>
+    <col min="2" max="2" width="56.1172" style="66" customWidth="1"/>
+    <col min="3" max="3" width="23.6719" style="66" customWidth="1"/>
+    <col min="4" max="4" width="47.2422" style="66" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="66" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="66" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+    <row r="1" ht="27.65" customHeight="1">
+      <c r="A1" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" t="s" s="6">
-        <v>264</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-    </row>
-    <row r="3" ht="32.05" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" t="s" s="11">
-        <v>265</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-    </row>
-    <row r="4" ht="32.05" customHeight="1">
-      <c r="A4" s="63"/>
+      <c r="A2" t="s" s="28">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>160</v>
+      </c>
+      <c r="C2" t="s" s="3">
+        <v>161</v>
+      </c>
+      <c r="D2" t="s" s="3">
+        <v>162</v>
+      </c>
+      <c r="E2" t="s" s="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" s="29">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s" s="6">
+        <v>165</v>
+      </c>
+      <c r="C3" t="s" s="7">
+        <v>229</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" t="s" s="7">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" ht="20.05" customHeight="1">
+      <c r="A4" s="30">
+        <v>2</v>
+      </c>
       <c r="B4" t="s" s="11">
-        <v>266</v>
+        <v>168</v>
       </c>
       <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
+      <c r="D4" t="s" s="12">
+        <v>267</v>
+      </c>
       <c r="E4" s="14"/>
     </row>
     <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" s="63"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
+      <c r="A5" s="30">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s" s="11">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s" s="12">
+        <v>269</v>
+      </c>
+      <c r="D5" t="s" s="12">
+        <v>270</v>
+      </c>
       <c r="E5" s="14"/>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="63"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="30">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s" s="11">
+        <v>271</v>
+      </c>
+      <c r="C6" t="s" s="12">
+        <v>272</v>
+      </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="54"/>
+      <c r="A7" s="30">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s" s="11">
+        <v>273</v>
+      </c>
       <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
+      <c r="D7" t="s" s="12">
+        <v>274</v>
+      </c>
       <c r="E7" s="14"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="54"/>
+      <c r="A8" s="30">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s" s="11">
+        <v>275</v>
+      </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
+      <c r="A9" s="30">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s" s="11">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s" s="12">
+        <v>277</v>
+      </c>
+      <c r="D9" t="s" s="12">
+        <v>278</v>
+      </c>
       <c r="E9" s="14"/>
     </row>
     <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="A10" s="30">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s" s="11">
+        <v>279</v>
+      </c>
+      <c r="C10" t="s" s="12">
+        <v>280</v>
+      </c>
+      <c r="D10" t="s" s="12">
+        <v>281</v>
+      </c>
+      <c r="E10" s="67"/>
+    </row>
+    <row r="11" ht="20.05" customHeight="1">
+      <c r="A11" s="30">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s" s="11">
+        <v>282</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" t="s" s="12">
+        <v>283</v>
+      </c>
+      <c r="E11" t="s" s="65">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" ht="20.05" customHeight="1">
+      <c r="A12" s="30">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s" s="11">
+        <v>210</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" t="s" s="12">
+        <v>284</v>
+      </c>
+      <c r="E12" t="s" s="49">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="13" ht="20.05" customHeight="1">
+      <c r="A13" s="30">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s" s="11">
+        <v>213</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" t="s" s="12">
+        <v>285</v>
+      </c>
+      <c r="E13" t="s" s="52">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" ht="20.05" customHeight="1">
+      <c r="A14" s="30">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s" s="11">
+        <v>216</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" t="s" s="12">
+        <v>286</v>
+      </c>
+      <c r="E14" t="s" s="53">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" ht="20.05" customHeight="1">
+      <c r="A15" s="30">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s" s="11">
+        <v>219</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" t="s" s="37">
+        <v>287</v>
+      </c>
+      <c r="E15" t="s" s="56">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" ht="20.05" customHeight="1">
+      <c r="A16" s="30">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="11">
+        <v>222</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+    </row>
+    <row r="17" ht="20.05" customHeight="1">
+      <c r="A17" s="31"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" ht="20.05" customHeight="1">
+      <c r="A18" s="31"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
@@ -7290,299 +9423,92 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E20"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="64" customWidth="1"/>
-    <col min="2" max="2" width="57.1719" style="64" customWidth="1"/>
-    <col min="3" max="3" width="33.8125" style="64" customWidth="1"/>
-    <col min="4" max="4" width="35.0781" style="64" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="64" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="64" customWidth="1"/>
+    <col min="1" max="1" width="16.3516" style="68" customWidth="1"/>
+    <col min="2" max="2" width="35.1484" style="68" customWidth="1"/>
+    <col min="3" max="5" width="16.3516" style="68" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.65" customHeight="1">
-      <c r="A1" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+    <row r="1" ht="20.25" customHeight="1">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" t="s" s="27">
-        <v>134</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>135</v>
-      </c>
-      <c r="C2" t="s" s="3">
-        <v>136</v>
-      </c>
-      <c r="D2" t="s" s="3">
-        <v>137</v>
-      </c>
-      <c r="E2" t="s" s="3">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="28">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s" s="6">
-        <v>140</v>
-      </c>
-      <c r="C3" t="s" s="7">
-        <v>203</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" t="s" s="7">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" ht="20.05" customHeight="1">
-      <c r="A4" s="29">
-        <v>2</v>
-      </c>
+      <c r="A2" s="69"/>
+      <c r="B2" t="s" s="6">
+        <v>288</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" ht="32.05" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" t="s" s="11">
+        <v>289</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+    </row>
+    <row r="4" ht="32.05" customHeight="1">
+      <c r="A4" s="70"/>
       <c r="B4" t="s" s="11">
-        <v>143</v>
+        <v>290</v>
       </c>
       <c r="C4" s="14"/>
-      <c r="D4" t="s" s="12">
-        <v>268</v>
-      </c>
+      <c r="D4" s="14"/>
       <c r="E4" s="14"/>
     </row>
     <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" s="29">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s" s="11">
-        <v>269</v>
-      </c>
+      <c r="A5" s="70"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="29">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s" s="11">
-        <v>270</v>
-      </c>
+      <c r="A6" s="70"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="14"/>
-      <c r="D6" t="s" s="12">
-        <v>271</v>
-      </c>
+      <c r="D6" s="14"/>
       <c r="E6" s="14"/>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="29">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s" s="11">
-        <v>205</v>
-      </c>
-      <c r="C7" t="s" s="12">
-        <v>206</v>
-      </c>
-      <c r="D7" t="s" s="12">
-        <v>272</v>
-      </c>
+      <c r="A7" s="70"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
       <c r="E7" s="14"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="29">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s" s="11">
-        <v>170</v>
-      </c>
-      <c r="C8" t="s" s="12">
-        <v>273</v>
-      </c>
-      <c r="D8" t="s" s="12">
-        <v>274</v>
-      </c>
-      <c r="E8" t="s" s="30">
-        <v>172</v>
-      </c>
+      <c r="A8" s="70"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="29">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s" s="11">
-        <v>173</v>
-      </c>
-      <c r="C9" t="s" s="12">
-        <v>273</v>
-      </c>
-      <c r="D9" t="s" s="33">
-        <v>275</v>
-      </c>
-      <c r="E9" t="s" s="34">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" ht="20.85" customHeight="1">
-      <c r="A10" s="29">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s" s="11">
-        <v>176</v>
-      </c>
-      <c r="C10" t="s" s="12">
-        <v>273</v>
-      </c>
-      <c r="D10" t="s" s="12">
-        <v>276</v>
-      </c>
-      <c r="E10" t="s" s="37">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" ht="21.7" customHeight="1">
-      <c r="A11" s="29">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s" s="11">
-        <v>179</v>
-      </c>
-      <c r="C11" t="s" s="12">
-        <v>273</v>
-      </c>
-      <c r="D11" t="s" s="38">
-        <v>277</v>
-      </c>
-      <c r="E11" t="s" s="39">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" ht="20.85" customHeight="1">
-      <c r="A12" s="29">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s" s="11">
-        <v>182</v>
-      </c>
-      <c r="C12" t="s" s="12">
-        <v>273</v>
-      </c>
-      <c r="D12" t="s" s="12">
-        <v>278</v>
-      </c>
-      <c r="E12" t="s" s="42">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="29">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s" s="11">
-        <v>185</v>
-      </c>
-      <c r="C13" t="s" s="12">
-        <v>273</v>
-      </c>
-      <c r="D13" t="s" s="12">
-        <v>279</v>
-      </c>
-      <c r="E13" t="s" s="45">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="29">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s" s="11">
-        <v>188</v>
-      </c>
-      <c r="C14" t="s" s="12">
-        <v>273</v>
-      </c>
-      <c r="D14" t="s" s="12">
-        <v>280</v>
-      </c>
-      <c r="E14" t="s" s="48">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="29">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s" s="11">
-        <v>191</v>
-      </c>
-      <c r="C15" t="s" s="12">
-        <v>273</v>
-      </c>
-      <c r="D15" t="s" s="12">
-        <v>281</v>
-      </c>
-      <c r="E15" t="s" s="65">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="29">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s" s="11">
-        <v>282</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="29">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s" s="11">
-        <v>283</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" t="s" s="12">
-        <v>284</v>
-      </c>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="29">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s" s="11">
-        <v>197</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-    </row>
-    <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="53"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="A9" s="70"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+    </row>
+    <row r="10" ht="20.05" customHeight="1">
+      <c r="A10" s="70"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
@@ -7596,20 +9522,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E15"/>
+  <dimension ref="A2:E20"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.10156" style="66" customWidth="1"/>
-    <col min="2" max="2" width="32.6719" style="66" customWidth="1"/>
-    <col min="3" max="3" width="23.6719" style="66" customWidth="1"/>
-    <col min="4" max="4" width="24.625" style="66" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="66" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="66" customWidth="1"/>
+    <col min="1" max="1" width="8.10156" style="71" customWidth="1"/>
+    <col min="2" max="2" width="57.1719" style="71" customWidth="1"/>
+    <col min="3" max="3" width="33.8125" style="71" customWidth="1"/>
+    <col min="4" max="4" width="35.0781" style="71" customWidth="1"/>
+    <col min="5" max="5" width="16.3516" style="71" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7617,28 +9543,28 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" t="s" s="27">
-        <v>134</v>
+      <c r="A2" t="s" s="28">
+        <v>135</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>138</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="28">
+      <c r="A3" s="29">
         <v>1</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s" s="7">
         <v>229</v>
@@ -7649,156 +9575,241 @@
       </c>
     </row>
     <row r="4" ht="20.05" customHeight="1">
-      <c r="A4" s="29">
+      <c r="A4" s="30">
         <v>2</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>286</v>
+        <v>168</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" t="s" s="12">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E4" s="14"/>
     </row>
     <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" s="29">
+      <c r="A5" s="30">
         <v>3</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>288</v>
-      </c>
-      <c r="C5" t="s" s="12">
-        <v>289</v>
-      </c>
-      <c r="D5" t="s" s="12">
-        <v>290</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
       <c r="E5" s="14"/>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="29">
+      <c r="A6" s="30">
         <v>4</v>
       </c>
       <c r="B6" t="s" s="11">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
+      <c r="D6" t="s" s="12">
+        <v>295</v>
+      </c>
       <c r="E6" s="14"/>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="29">
+      <c r="A7" s="30">
         <v>5</v>
       </c>
       <c r="B7" t="s" s="11">
-        <v>292</v>
-      </c>
-      <c r="C7" s="14"/>
+        <v>231</v>
+      </c>
+      <c r="C7" t="s" s="12">
+        <v>296</v>
+      </c>
       <c r="D7" t="s" s="12">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E7" s="14"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="29">
+      <c r="A8" s="30">
         <v>6</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>294</v>
-      </c>
-      <c r="C8" s="14"/>
+        <v>195</v>
+      </c>
+      <c r="C8" t="s" s="12">
+        <v>298</v>
+      </c>
       <c r="D8" t="s" s="12">
-        <v>295</v>
-      </c>
-      <c r="E8" s="14"/>
+        <v>299</v>
+      </c>
+      <c r="E8" t="s" s="34">
+        <v>197</v>
+      </c>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="29">
+      <c r="A9" s="30">
         <v>7</v>
       </c>
       <c r="B9" t="s" s="11">
-        <v>296</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" t="s" s="12">
-        <v>297</v>
-      </c>
-      <c r="E9" s="14"/>
-    </row>
-    <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="29">
+        <v>198</v>
+      </c>
+      <c r="C9" t="s" s="12">
+        <v>298</v>
+      </c>
+      <c r="D9" t="s" s="37">
+        <v>300</v>
+      </c>
+      <c r="E9" t="s" s="38">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" ht="20.85" customHeight="1">
+      <c r="A10" s="30">
         <v>8</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>185</v>
-      </c>
-      <c r="C10" s="14"/>
+        <v>201</v>
+      </c>
+      <c r="C10" t="s" s="12">
+        <v>298</v>
+      </c>
       <c r="D10" t="s" s="12">
+        <v>301</v>
+      </c>
+      <c r="E10" t="s" s="41">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" ht="21.7" customHeight="1">
+      <c r="A11" s="30">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s" s="11">
+        <v>204</v>
+      </c>
+      <c r="C11" t="s" s="12">
         <v>298</v>
       </c>
-      <c r="E10" t="s" s="45">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="29">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s" s="11">
-        <v>299</v>
-      </c>
-      <c r="C11" t="s" s="12">
-        <v>159</v>
-      </c>
-      <c r="D11" t="s" s="12">
-        <v>300</v>
-      </c>
-      <c r="E11" t="s" s="48">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="29">
+      <c r="D11" t="s" s="42">
+        <v>302</v>
+      </c>
+      <c r="E11" t="s" s="43">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" ht="20.85" customHeight="1">
+      <c r="A12" s="30">
         <v>10</v>
       </c>
       <c r="B12" t="s" s="11">
-        <v>301</v>
+        <v>207</v>
       </c>
       <c r="C12" t="s" s="12">
-        <v>159</v>
+        <v>298</v>
       </c>
       <c r="D12" t="s" s="12">
-        <v>302</v>
-      </c>
-      <c r="E12" t="s" s="65">
-        <v>193</v>
+        <v>303</v>
+      </c>
+      <c r="E12" t="s" s="46">
+        <v>209</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="29">
+      <c r="A13" s="30">
         <v>11</v>
       </c>
       <c r="B13" t="s" s="11">
-        <v>197</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="C13" t="s" s="12">
+        <v>298</v>
+      </c>
+      <c r="D13" t="s" s="12">
+        <v>304</v>
+      </c>
+      <c r="E13" t="s" s="49">
+        <v>212</v>
+      </c>
     </row>
     <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="A14" s="30">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s" s="11">
+        <v>213</v>
+      </c>
+      <c r="C14" t="s" s="12">
+        <v>298</v>
+      </c>
+      <c r="D14" t="s" s="12">
+        <v>305</v>
+      </c>
+      <c r="E14" t="s" s="52">
+        <v>215</v>
+      </c>
     </row>
     <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="30">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s" s="11">
+        <v>216</v>
+      </c>
+      <c r="C15" t="s" s="12">
+        <v>298</v>
+      </c>
+      <c r="D15" t="s" s="12">
+        <v>306</v>
+      </c>
+      <c r="E15" t="s" s="72">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" ht="20.05" customHeight="1">
+      <c r="A16" s="30">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="11">
+        <v>307</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+    </row>
+    <row r="17" ht="20.05" customHeight="1">
+      <c r="A17" s="30">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s" s="11">
+        <v>308</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" t="s" s="12">
+        <v>309</v>
+      </c>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" ht="20.05" customHeight="1">
+      <c r="A18" s="30">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s" s="11">
+        <v>222</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+    </row>
+    <row r="19" ht="20.05" customHeight="1">
+      <c r="A19" s="31"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+    </row>
+    <row r="20" ht="20.05" customHeight="1">
+      <c r="A20" s="31"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
